--- a/DATOS/Datos procesados/Censo 2022 - Vicente López.xlsx
+++ b/DATOS/Datos procesados/Censo 2022 - Vicente López.xlsx
@@ -9,16 +9,19 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="WYlueJLDsH35bKsdmKFy/0YVuNsIKpDx55r0IC22EEk="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="sWGVoQATAyQcF/NeL9cgsMElGKsuIclqakp8gBaj0vY="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="67">
   <si>
     <t>Municipios</t>
+  </si>
+  <si>
+    <t>Total de población</t>
   </si>
   <si>
     <t>Localidades</t>
@@ -293,11 +296,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -317,6 +323,9 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="1"/>
@@ -547,14 +556,14 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="61.0"/>
+    <col customWidth="1" min="4" max="4" width="61.0"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -563,1390 +572,1420 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AA1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AB1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AD1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AE1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AF1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AG1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AH1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AI1" s="6" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AK1" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="5" t="s">
+      <c r="AL1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="5" t="s">
+      <c r="AM1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="5" t="s">
+      <c r="AN1" s="6" t="s">
         <v>39</v>
       </c>
       <c r="AO1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AP1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AQ1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AR1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AS1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AT1" s="7" t="s">
         <v>45</v>
+      </c>
+      <c r="AU1" s="7" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>47</v>
+      </c>
+      <c r="B2" s="9">
+        <v>280541.0</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="12">
         <v>6995.0</v>
       </c>
-      <c r="F2" s="10">
+      <c r="G2" s="12">
         <v>16914.0</v>
       </c>
-      <c r="G2" s="11">
+      <c r="H2" s="13">
         <v>8910.0</v>
       </c>
-      <c r="H2" s="11">
+      <c r="I2" s="13">
         <v>8004.0</v>
       </c>
-      <c r="I2" s="11">
+      <c r="J2" s="13">
         <v>681.0</v>
       </c>
-      <c r="J2" s="11">
+      <c r="K2" s="13">
         <v>939.0</v>
       </c>
-      <c r="K2" s="11">
+      <c r="L2" s="13">
         <v>1101.0</v>
       </c>
-      <c r="L2" s="11">
+      <c r="M2" s="13">
         <v>1090.0</v>
       </c>
-      <c r="M2" s="11">
+      <c r="N2" s="13">
         <v>999.0</v>
       </c>
-      <c r="N2" s="11">
+      <c r="O2" s="13">
         <v>865.0</v>
       </c>
-      <c r="O2" s="11">
+      <c r="P2" s="13">
         <v>939.0</v>
       </c>
-      <c r="P2" s="11">
+      <c r="Q2" s="13">
         <v>1118.0</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="R2" s="13">
         <v>1364.0</v>
       </c>
-      <c r="R2" s="11">
+      <c r="S2" s="13">
         <v>1391.0</v>
       </c>
-      <c r="S2" s="11">
+      <c r="T2" s="13">
         <v>1137.0</v>
       </c>
-      <c r="T2" s="11">
+      <c r="U2" s="13">
         <v>1019.0</v>
       </c>
-      <c r="U2" s="11">
+      <c r="V2" s="13">
         <v>956.0</v>
       </c>
-      <c r="V2" s="11">
+      <c r="W2" s="13">
         <v>914.0</v>
       </c>
-      <c r="W2" s="11">
+      <c r="X2" s="13">
         <v>838.0</v>
       </c>
-      <c r="X2" s="11">
+      <c r="Y2" s="13">
         <v>687.0</v>
       </c>
-      <c r="Y2" s="11">
+      <c r="Z2" s="13">
         <v>449.0</v>
       </c>
-      <c r="Z2" s="11">
+      <c r="AA2" s="13">
         <v>267.0</v>
       </c>
-      <c r="AA2" s="11">
+      <c r="AB2" s="13">
         <v>127.0</v>
       </c>
-      <c r="AB2" s="11">
+      <c r="AC2" s="13">
         <v>31.0</v>
       </c>
-      <c r="AC2" s="11">
+      <c r="AD2" s="13">
         <v>2.0</v>
       </c>
-      <c r="AD2" s="11">
+      <c r="AE2" s="13">
         <v>6509.0</v>
       </c>
-      <c r="AE2" s="11">
+      <c r="AF2" s="13">
         <v>26.0</v>
       </c>
-      <c r="AF2" s="11">
+      <c r="AG2" s="13">
         <v>2.0</v>
       </c>
-      <c r="AG2" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH2" s="11">
+      <c r="AH2" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI2" s="13">
         <v>1.0</v>
       </c>
-      <c r="AI2" s="11">
+      <c r="AJ2" s="13">
         <v>40.0</v>
       </c>
-      <c r="AJ2" s="11">
+      <c r="AK2" s="13">
         <v>5981.0</v>
       </c>
-      <c r="AK2" s="11">
+      <c r="AL2" s="13">
         <v>597.0</v>
       </c>
-      <c r="AL2" s="11">
+      <c r="AM2" s="13">
         <v>14271.0</v>
       </c>
-      <c r="AM2" s="11">
+      <c r="AN2" s="13">
         <v>227.0</v>
       </c>
-      <c r="AN2" s="11">
+      <c r="AO2" s="13">
         <v>2416.0</v>
       </c>
-      <c r="AO2" s="11">
+      <c r="AP2" s="13">
         <v>5131.0</v>
       </c>
-      <c r="AP2" s="11">
+      <c r="AQ2" s="13">
         <v>11463.0</v>
       </c>
-      <c r="AQ2" s="11">
+      <c r="AR2" s="13">
         <v>320.0</v>
       </c>
-      <c r="AR2" s="11">
+      <c r="AS2" s="13">
         <v>8507.0</v>
       </c>
-      <c r="AS2" s="11">
+      <c r="AT2" s="13">
         <v>722.0</v>
       </c>
-      <c r="AT2" s="11">
+      <c r="AU2" s="13">
         <v>5184.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="A3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="9">
+        <v>280541.0</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="10">
+      <c r="D3" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="12">
         <v>22270.0</v>
       </c>
-      <c r="F3" s="10">
+      <c r="G3" s="12">
         <v>49536.0</v>
       </c>
-      <c r="G3" s="11">
+      <c r="H3" s="13">
         <v>26765.0</v>
       </c>
-      <c r="H3" s="11">
+      <c r="I3" s="13">
         <v>22771.0</v>
       </c>
-      <c r="I3" s="11">
+      <c r="J3" s="13">
         <v>2083.0</v>
       </c>
-      <c r="J3" s="11">
+      <c r="K3" s="13">
         <v>2563.0</v>
       </c>
-      <c r="K3" s="11">
+      <c r="L3" s="13">
         <v>3041.0</v>
       </c>
-      <c r="L3" s="11">
+      <c r="M3" s="13">
         <v>3155.0</v>
       </c>
-      <c r="M3" s="11">
+      <c r="N3" s="13">
         <v>2895.0</v>
       </c>
-      <c r="N3" s="11">
+      <c r="O3" s="13">
         <v>2741.0</v>
       </c>
-      <c r="O3" s="11">
+      <c r="P3" s="13">
         <v>3087.0</v>
       </c>
-      <c r="P3" s="11">
+      <c r="Q3" s="13">
         <v>3502.0</v>
       </c>
-      <c r="Q3" s="11">
+      <c r="R3" s="13">
         <v>3652.0</v>
       </c>
-      <c r="R3" s="11">
+      <c r="S3" s="13">
         <v>3821.0</v>
       </c>
-      <c r="S3" s="11">
+      <c r="T3" s="13">
         <v>3329.0</v>
       </c>
-      <c r="T3" s="11">
+      <c r="U3" s="13">
         <v>3086.0</v>
       </c>
-      <c r="U3" s="11">
+      <c r="V3" s="13">
         <v>3009.0</v>
       </c>
-      <c r="V3" s="11">
+      <c r="W3" s="13">
         <v>2406.0</v>
       </c>
-      <c r="W3" s="11">
+      <c r="X3" s="13">
         <v>2284.0</v>
       </c>
-      <c r="X3" s="11">
+      <c r="Y3" s="13">
         <v>1974.0</v>
       </c>
-      <c r="Y3" s="11">
+      <c r="Z3" s="13">
         <v>1428.0</v>
       </c>
-      <c r="Z3" s="11">
+      <c r="AA3" s="13">
         <v>919.0</v>
       </c>
-      <c r="AA3" s="11">
+      <c r="AB3" s="13">
         <v>449.0</v>
       </c>
-      <c r="AB3" s="11">
+      <c r="AC3" s="13">
         <v>102.0</v>
       </c>
-      <c r="AC3" s="11">
+      <c r="AD3" s="13">
         <v>10.0</v>
       </c>
-      <c r="AD3" s="11">
+      <c r="AE3" s="13">
         <v>20246.0</v>
       </c>
-      <c r="AE3" s="11">
+      <c r="AF3" s="13">
         <v>100.0</v>
       </c>
-      <c r="AF3" s="11">
+      <c r="AG3" s="13">
         <v>39.0</v>
       </c>
-      <c r="AG3" s="11">
+      <c r="AH3" s="13">
         <v>25.0</v>
       </c>
-      <c r="AH3" s="11">
+      <c r="AI3" s="13">
         <v>22.0</v>
       </c>
-      <c r="AI3" s="11">
+      <c r="AJ3" s="13">
         <v>157.0</v>
       </c>
-      <c r="AJ3" s="11">
+      <c r="AK3" s="13">
         <v>19133.0</v>
       </c>
-      <c r="AK3" s="11">
+      <c r="AL3" s="13">
         <v>1456.0</v>
       </c>
-      <c r="AL3" s="11">
+      <c r="AM3" s="13">
         <v>44666.0</v>
       </c>
-      <c r="AM3" s="11">
+      <c r="AN3" s="13">
         <v>733.0</v>
       </c>
-      <c r="AN3" s="11">
+      <c r="AO3" s="13">
         <v>4137.0</v>
       </c>
-      <c r="AO3" s="11">
+      <c r="AP3" s="13">
         <v>15196.0</v>
       </c>
-      <c r="AP3" s="11">
+      <c r="AQ3" s="13">
         <v>32648.0</v>
       </c>
-      <c r="AQ3" s="11">
+      <c r="AR3" s="13">
         <v>1692.0</v>
       </c>
-      <c r="AR3" s="11">
+      <c r="AS3" s="13">
         <v>25955.0</v>
       </c>
-      <c r="AS3" s="11">
+      <c r="AT3" s="13">
         <v>2311.0</v>
       </c>
-      <c r="AT3" s="11">
+      <c r="AU3" s="13">
         <v>14243.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>53</v>
+      <c r="A4" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="9">
+        <v>280541.0</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="10">
+      <c r="D4" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="12">
         <v>11524.0</v>
       </c>
-      <c r="F4" s="10">
+      <c r="G4" s="12">
         <v>28227.0</v>
       </c>
-      <c r="G4" s="11">
+      <c r="H4" s="13">
         <v>14713.0</v>
       </c>
-      <c r="H4" s="11">
+      <c r="I4" s="13">
         <v>13514.0</v>
       </c>
-      <c r="I4" s="11">
+      <c r="J4" s="13">
         <v>1268.0</v>
       </c>
-      <c r="J4" s="11">
+      <c r="K4" s="13">
         <v>1889.0</v>
       </c>
-      <c r="K4" s="11">
+      <c r="L4" s="13">
         <v>1992.0</v>
       </c>
-      <c r="L4" s="11">
+      <c r="M4" s="13">
         <v>1937.0</v>
       </c>
-      <c r="M4" s="11">
+      <c r="N4" s="13">
         <v>1792.0</v>
       </c>
-      <c r="N4" s="11">
+      <c r="O4" s="13">
         <v>1731.0</v>
       </c>
-      <c r="O4" s="11">
+      <c r="P4" s="13">
         <v>1970.0</v>
       </c>
-      <c r="P4" s="11">
+      <c r="Q4" s="13">
         <v>2137.0</v>
       </c>
-      <c r="Q4" s="11">
+      <c r="R4" s="13">
         <v>2169.0</v>
       </c>
-      <c r="R4" s="11">
+      <c r="S4" s="13">
         <v>2003.0</v>
       </c>
-      <c r="S4" s="11">
+      <c r="T4" s="13">
         <v>1766.0</v>
       </c>
-      <c r="T4" s="11">
+      <c r="U4" s="13">
         <v>1540.0</v>
       </c>
-      <c r="U4" s="11">
+      <c r="V4" s="13">
         <v>1499.0</v>
       </c>
-      <c r="V4" s="11">
+      <c r="W4" s="13">
         <v>1324.0</v>
       </c>
-      <c r="W4" s="11">
+      <c r="X4" s="13">
         <v>1177.0</v>
       </c>
-      <c r="X4" s="11">
+      <c r="Y4" s="13">
         <v>857.0</v>
       </c>
-      <c r="Y4" s="11">
+      <c r="Z4" s="13">
         <v>589.0</v>
       </c>
-      <c r="Z4" s="11">
+      <c r="AA4" s="13">
         <v>352.0</v>
       </c>
-      <c r="AA4" s="11">
+      <c r="AB4" s="13">
         <v>163.0</v>
       </c>
-      <c r="AB4" s="11">
+      <c r="AC4" s="13">
         <v>61.0</v>
       </c>
-      <c r="AC4" s="11">
+      <c r="AD4" s="13">
         <v>11.0</v>
       </c>
-      <c r="AD4" s="11">
+      <c r="AE4" s="13">
         <v>10484.0</v>
       </c>
-      <c r="AE4" s="11">
+      <c r="AF4" s="13">
         <v>97.0</v>
       </c>
-      <c r="AF4" s="11">
+      <c r="AG4" s="13">
         <v>4.0</v>
       </c>
-      <c r="AG4" s="11">
+      <c r="AH4" s="13">
         <v>11.0</v>
       </c>
-      <c r="AH4" s="11">
+      <c r="AI4" s="13">
         <v>5.0</v>
       </c>
-      <c r="AI4" s="11">
+      <c r="AJ4" s="13">
         <v>70.0</v>
       </c>
-      <c r="AJ4" s="11">
+      <c r="AK4" s="13">
         <v>9387.0</v>
       </c>
-      <c r="AK4" s="11">
+      <c r="AL4" s="13">
         <v>1284.0</v>
       </c>
-      <c r="AL4" s="11">
+      <c r="AM4" s="13">
         <v>20721.0</v>
       </c>
-      <c r="AM4" s="11">
+      <c r="AN4" s="13">
         <v>650.0</v>
       </c>
-      <c r="AN4" s="11">
+      <c r="AO4" s="13">
         <v>6856.0</v>
       </c>
-      <c r="AO4" s="11">
+      <c r="AP4" s="13">
         <v>9021.0</v>
       </c>
-      <c r="AP4" s="11">
+      <c r="AQ4" s="13">
         <v>18445.0</v>
       </c>
-      <c r="AQ4" s="11">
+      <c r="AR4" s="13">
         <v>761.0</v>
       </c>
-      <c r="AR4" s="11">
+      <c r="AS4" s="13">
         <v>14289.0</v>
       </c>
-      <c r="AS4" s="11">
+      <c r="AT4" s="13">
         <v>1237.0</v>
       </c>
-      <c r="AT4" s="11">
+      <c r="AU4" s="13">
         <v>7936.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>55</v>
+      <c r="A5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="9">
+        <v>280541.0</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="10">
+      <c r="D5" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="12">
         <v>6321.0</v>
       </c>
-      <c r="F5" s="10">
+      <c r="G5" s="12">
         <v>13554.0</v>
       </c>
-      <c r="G5" s="11">
+      <c r="H5" s="13">
         <v>7236.0</v>
       </c>
-      <c r="H5" s="11">
+      <c r="I5" s="13">
         <v>6318.0</v>
       </c>
-      <c r="I5" s="11">
+      <c r="J5" s="13">
         <v>609.0</v>
       </c>
-      <c r="J5" s="11">
+      <c r="K5" s="13">
         <v>710.0</v>
       </c>
-      <c r="K5" s="11">
+      <c r="L5" s="13">
         <v>781.0</v>
       </c>
-      <c r="L5" s="11">
+      <c r="M5" s="13">
         <v>822.0</v>
       </c>
-      <c r="M5" s="11">
+      <c r="N5" s="13">
         <v>781.0</v>
       </c>
-      <c r="N5" s="11">
+      <c r="O5" s="13">
         <v>720.0</v>
       </c>
-      <c r="O5" s="11">
+      <c r="P5" s="13">
         <v>790.0</v>
       </c>
-      <c r="P5" s="11">
+      <c r="Q5" s="13">
         <v>880.0</v>
       </c>
-      <c r="Q5" s="11">
+      <c r="R5" s="13">
         <v>1004.0</v>
       </c>
-      <c r="R5" s="11">
+      <c r="S5" s="13">
         <v>1012.0</v>
       </c>
-      <c r="S5" s="11">
+      <c r="T5" s="13">
         <v>932.0</v>
       </c>
-      <c r="T5" s="11">
+      <c r="U5" s="13">
         <v>797.0</v>
       </c>
-      <c r="U5" s="11">
+      <c r="V5" s="13">
         <v>851.0</v>
       </c>
-      <c r="V5" s="11">
+      <c r="W5" s="13">
         <v>727.0</v>
       </c>
-      <c r="W5" s="11">
+      <c r="X5" s="13">
         <v>732.0</v>
       </c>
-      <c r="X5" s="11">
+      <c r="Y5" s="13">
         <v>574.0</v>
       </c>
-      <c r="Y5" s="11">
+      <c r="Z5" s="13">
         <v>394.0</v>
       </c>
-      <c r="Z5" s="11">
+      <c r="AA5" s="13">
         <v>259.0</v>
       </c>
-      <c r="AA5" s="11">
+      <c r="AB5" s="13">
         <v>140.0</v>
       </c>
-      <c r="AB5" s="11">
+      <c r="AC5" s="13">
         <v>36.0</v>
       </c>
-      <c r="AC5" s="11">
+      <c r="AD5" s="13">
         <v>3.0</v>
       </c>
-      <c r="AD5" s="11">
+      <c r="AE5" s="13">
         <v>5466.0</v>
       </c>
-      <c r="AE5" s="11">
+      <c r="AF5" s="13">
         <v>53.0</v>
       </c>
-      <c r="AF5" s="11">
+      <c r="AG5" s="13">
         <v>7.0</v>
       </c>
-      <c r="AG5" s="11">
+      <c r="AH5" s="13">
         <v>3.0</v>
       </c>
-      <c r="AH5" s="11">
+      <c r="AI5" s="13">
         <v>6.0</v>
       </c>
-      <c r="AI5" s="11">
+      <c r="AJ5" s="13">
         <v>33.0</v>
       </c>
-      <c r="AJ5" s="11">
+      <c r="AK5" s="13">
         <v>5227.0</v>
       </c>
-      <c r="AK5" s="11">
+      <c r="AL5" s="13">
         <v>341.0</v>
       </c>
-      <c r="AL5" s="11">
+      <c r="AM5" s="13">
         <v>12426.0</v>
       </c>
-      <c r="AM5" s="11">
+      <c r="AN5" s="13">
         <v>176.0</v>
       </c>
-      <c r="AN5" s="11">
+      <c r="AO5" s="13">
         <v>952.0</v>
       </c>
-      <c r="AO5" s="11">
+      <c r="AP5" s="13">
         <v>4000.0</v>
       </c>
-      <c r="AP5" s="11">
+      <c r="AQ5" s="13">
         <v>8923.0</v>
       </c>
-      <c r="AQ5" s="11">
+      <c r="AR5" s="13">
         <v>631.0</v>
       </c>
-      <c r="AR5" s="11">
+      <c r="AS5" s="13">
         <v>6897.0</v>
       </c>
-      <c r="AS5" s="11">
+      <c r="AT5" s="13">
         <v>646.0</v>
       </c>
-      <c r="AT5" s="11">
+      <c r="AU5" s="13">
         <v>4077.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>57</v>
+      <c r="A6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="9">
+        <v>280541.0</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="10">
+      <c r="D6" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="12">
         <v>14580.0</v>
       </c>
-      <c r="F6" s="10">
+      <c r="G6" s="12">
         <v>34797.0</v>
       </c>
-      <c r="G6" s="11">
+      <c r="H6" s="13">
         <v>18277.0</v>
       </c>
-      <c r="H6" s="11">
+      <c r="I6" s="13">
         <v>16520.0</v>
       </c>
-      <c r="I6" s="11">
+      <c r="J6" s="13">
         <v>1502.0</v>
       </c>
-      <c r="J6" s="11">
+      <c r="K6" s="13">
         <v>2037.0</v>
       </c>
-      <c r="K6" s="11">
+      <c r="L6" s="13">
         <v>2099.0</v>
       </c>
-      <c r="L6" s="11">
+      <c r="M6" s="13">
         <v>2258.0</v>
       </c>
-      <c r="M6" s="11">
+      <c r="N6" s="13">
         <v>2169.0</v>
       </c>
-      <c r="N6" s="11">
+      <c r="O6" s="13">
         <v>2158.0</v>
       </c>
-      <c r="O6" s="11">
+      <c r="P6" s="13">
         <v>2461.0</v>
       </c>
-      <c r="P6" s="11">
+      <c r="Q6" s="13">
         <v>2584.0</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="R6" s="13">
         <v>2800.0</v>
       </c>
-      <c r="R6" s="11">
+      <c r="S6" s="13">
         <v>2539.0</v>
       </c>
-      <c r="S6" s="11">
+      <c r="T6" s="13">
         <v>2346.0</v>
       </c>
-      <c r="T6" s="11">
+      <c r="U6" s="13">
         <v>1963.0</v>
       </c>
-      <c r="U6" s="11">
+      <c r="V6" s="13">
         <v>1877.0</v>
       </c>
-      <c r="V6" s="11">
+      <c r="W6" s="13">
         <v>1705.0</v>
       </c>
-      <c r="W6" s="11">
+      <c r="X6" s="13">
         <v>1490.0</v>
       </c>
-      <c r="X6" s="11">
+      <c r="Y6" s="13">
         <v>1163.0</v>
       </c>
-      <c r="Y6" s="11">
+      <c r="Z6" s="13">
         <v>815.0</v>
       </c>
-      <c r="Z6" s="11">
+      <c r="AA6" s="13">
         <v>542.0</v>
       </c>
-      <c r="AA6" s="11">
+      <c r="AB6" s="13">
         <v>222.0</v>
       </c>
-      <c r="AB6" s="11">
+      <c r="AC6" s="13">
         <v>63.0</v>
       </c>
-      <c r="AC6" s="11">
+      <c r="AD6" s="13">
         <v>4.0</v>
       </c>
-      <c r="AD6" s="11">
+      <c r="AE6" s="13">
         <v>13481.0</v>
       </c>
-      <c r="AE6" s="11">
+      <c r="AF6" s="13">
         <v>45.0</v>
       </c>
-      <c r="AF6" s="11">
+      <c r="AG6" s="13">
         <v>4.0</v>
       </c>
-      <c r="AG6" s="11">
+      <c r="AH6" s="13">
         <v>3.0</v>
       </c>
-      <c r="AH6" s="11">
+      <c r="AI6" s="13">
         <v>12.0</v>
       </c>
-      <c r="AI6" s="11">
+      <c r="AJ6" s="13">
         <v>100.0</v>
       </c>
-      <c r="AJ6" s="11">
+      <c r="AK6" s="13">
         <v>12097.0</v>
       </c>
-      <c r="AK6" s="11">
+      <c r="AL6" s="13">
         <v>1548.0</v>
       </c>
-      <c r="AL6" s="11">
+      <c r="AM6" s="13">
         <v>26894.0</v>
       </c>
-      <c r="AM6" s="11">
+      <c r="AN6" s="13">
         <v>640.0</v>
       </c>
-      <c r="AN6" s="11">
+      <c r="AO6" s="13">
         <v>7263.0</v>
       </c>
-      <c r="AO6" s="11">
+      <c r="AP6" s="13">
         <v>10561.0</v>
       </c>
-      <c r="AP6" s="11">
+      <c r="AQ6" s="13">
         <v>23259.0</v>
       </c>
-      <c r="AQ6" s="11">
+      <c r="AR6" s="13">
         <v>977.0</v>
       </c>
-      <c r="AR6" s="11">
+      <c r="AS6" s="13">
         <v>17970.0</v>
       </c>
-      <c r="AS6" s="11">
+      <c r="AT6" s="13">
         <v>1656.0</v>
       </c>
-      <c r="AT6" s="11">
+      <c r="AU6" s="13">
         <v>9979.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>59</v>
+      <c r="A7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="9">
+        <v>280541.0</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="10">
+      <c r="D7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="12">
         <v>36530.0</v>
       </c>
-      <c r="F7" s="10">
+      <c r="G7" s="12">
         <v>77296.0</v>
       </c>
-      <c r="G7" s="11">
+      <c r="H7" s="13">
         <v>41612.0</v>
       </c>
-      <c r="H7" s="11">
+      <c r="I7" s="13">
         <v>35684.0</v>
       </c>
-      <c r="I7" s="11">
+      <c r="J7" s="13">
         <v>3189.0</v>
       </c>
-      <c r="J7" s="11">
+      <c r="K7" s="13">
         <v>4075.0</v>
       </c>
-      <c r="K7" s="11">
+      <c r="L7" s="13">
         <v>4323.0</v>
       </c>
-      <c r="L7" s="11">
+      <c r="M7" s="13">
         <v>4756.0</v>
       </c>
-      <c r="M7" s="11">
+      <c r="N7" s="13">
         <v>4384.0</v>
       </c>
-      <c r="N7" s="11">
+      <c r="O7" s="13">
         <v>4234.0</v>
       </c>
-      <c r="O7" s="11">
+      <c r="P7" s="13">
         <v>4857.0</v>
       </c>
-      <c r="P7" s="11">
+      <c r="Q7" s="13">
         <v>5339.0</v>
       </c>
-      <c r="Q7" s="11">
+      <c r="R7" s="13">
         <v>5690.0</v>
       </c>
-      <c r="R7" s="11">
+      <c r="S7" s="13">
         <v>5942.0</v>
       </c>
-      <c r="S7" s="11">
+      <c r="T7" s="13">
         <v>5183.0</v>
       </c>
-      <c r="T7" s="11">
+      <c r="U7" s="13">
         <v>4895.0</v>
       </c>
-      <c r="U7" s="11">
+      <c r="V7" s="13">
         <v>4784.0</v>
       </c>
-      <c r="V7" s="11">
+      <c r="W7" s="13">
         <v>4171.0</v>
       </c>
-      <c r="W7" s="11">
+      <c r="X7" s="13">
         <v>3954.0</v>
       </c>
-      <c r="X7" s="11">
+      <c r="Y7" s="13">
         <v>3132.0</v>
       </c>
-      <c r="Y7" s="11">
+      <c r="Z7" s="13">
         <v>2118.0</v>
       </c>
-      <c r="Z7" s="11">
+      <c r="AA7" s="13">
         <v>1308.0</v>
       </c>
-      <c r="AA7" s="11">
+      <c r="AB7" s="13">
         <v>701.0</v>
       </c>
-      <c r="AB7" s="11">
+      <c r="AC7" s="13">
         <v>240.0</v>
       </c>
-      <c r="AC7" s="11">
+      <c r="AD7" s="13">
         <v>21.0</v>
       </c>
-      <c r="AD7" s="11">
+      <c r="AE7" s="13">
         <v>32425.0</v>
       </c>
-      <c r="AE7" s="11">
+      <c r="AF7" s="13">
         <v>128.0</v>
       </c>
-      <c r="AF7" s="11">
+      <c r="AG7" s="13">
         <v>19.0</v>
       </c>
-      <c r="AG7" s="11">
+      <c r="AH7" s="13">
         <v>9.0</v>
       </c>
-      <c r="AH7" s="11">
+      <c r="AI7" s="13">
         <v>22.0</v>
       </c>
-      <c r="AI7" s="11">
+      <c r="AJ7" s="13">
         <v>179.0</v>
       </c>
-      <c r="AJ7" s="11">
+      <c r="AK7" s="13">
         <v>30431.0</v>
       </c>
-      <c r="AK7" s="11">
+      <c r="AL7" s="13">
         <v>2351.0</v>
       </c>
-      <c r="AL7" s="11">
+      <c r="AM7" s="13">
         <v>68629.0</v>
       </c>
-      <c r="AM7" s="11">
+      <c r="AN7" s="13">
         <v>1068.0</v>
       </c>
-      <c r="AN7" s="11">
+      <c r="AO7" s="13">
         <v>7599.0</v>
       </c>
-      <c r="AO7" s="11">
+      <c r="AP7" s="13">
         <v>22946.0</v>
       </c>
-      <c r="AP7" s="11">
+      <c r="AQ7" s="13">
         <v>52574.0</v>
       </c>
-      <c r="AQ7" s="11">
+      <c r="AR7" s="13">
         <v>1776.0</v>
       </c>
-      <c r="AR7" s="11">
+      <c r="AS7" s="13">
         <v>40877.0</v>
       </c>
-      <c r="AS7" s="11">
+      <c r="AT7" s="13">
         <v>2988.0</v>
       </c>
-      <c r="AT7" s="11">
+      <c r="AU7" s="13">
         <v>22731.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>46</v>
+      <c r="A8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="9">
+        <v>280541.0</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="10">
+        <v>47</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="12">
         <v>12830.0</v>
       </c>
-      <c r="F8" s="10">
+      <c r="G8" s="12">
         <v>24790.0</v>
       </c>
-      <c r="G8" s="11">
+      <c r="H8" s="13">
         <v>13371.0</v>
       </c>
-      <c r="H8" s="11">
+      <c r="I8" s="13">
         <v>11419.0</v>
       </c>
-      <c r="I8" s="11">
+      <c r="J8" s="13">
         <v>1080.0</v>
       </c>
-      <c r="J8" s="11">
+      <c r="K8" s="13">
         <v>1188.0</v>
       </c>
-      <c r="K8" s="11">
+      <c r="L8" s="13">
         <v>1363.0</v>
       </c>
-      <c r="L8" s="11">
+      <c r="M8" s="13">
         <v>1361.0</v>
       </c>
-      <c r="M8" s="11">
+      <c r="N8" s="13">
         <v>1340.0</v>
       </c>
-      <c r="N8" s="11">
+      <c r="O8" s="13">
         <v>1506.0</v>
       </c>
-      <c r="O8" s="11">
+      <c r="P8" s="13">
         <v>1704.0</v>
       </c>
-      <c r="P8" s="11">
+      <c r="Q8" s="13">
         <v>1818.0</v>
       </c>
-      <c r="Q8" s="11">
+      <c r="R8" s="13">
         <v>1753.0</v>
       </c>
-      <c r="R8" s="11">
+      <c r="S8" s="13">
         <v>1740.0</v>
       </c>
-      <c r="S8" s="11">
+      <c r="T8" s="13">
         <v>1616.0</v>
       </c>
-      <c r="T8" s="11">
+      <c r="U8" s="13">
         <v>1537.0</v>
       </c>
-      <c r="U8" s="11">
+      <c r="V8" s="13">
         <v>1454.0</v>
       </c>
-      <c r="V8" s="11">
+      <c r="W8" s="13">
         <v>1306.0</v>
       </c>
-      <c r="W8" s="11">
+      <c r="X8" s="13">
         <v>1336.0</v>
       </c>
-      <c r="X8" s="11">
+      <c r="Y8" s="13">
         <v>1154.0</v>
       </c>
-      <c r="Y8" s="11">
+      <c r="Z8" s="13">
         <v>780.0</v>
       </c>
-      <c r="Z8" s="11">
+      <c r="AA8" s="13">
         <v>456.0</v>
       </c>
-      <c r="AA8" s="11">
+      <c r="AB8" s="13">
         <v>232.0</v>
       </c>
-      <c r="AB8" s="11">
+      <c r="AC8" s="13">
         <v>56.0</v>
       </c>
-      <c r="AC8" s="11">
+      <c r="AD8" s="13">
         <v>10.0</v>
       </c>
-      <c r="AD8" s="11">
+      <c r="AE8" s="13">
         <v>11192.0</v>
       </c>
-      <c r="AE8" s="11">
+      <c r="AF8" s="13">
         <v>42.0</v>
       </c>
-      <c r="AF8" s="11">
+      <c r="AG8" s="13">
         <v>7.0</v>
       </c>
-      <c r="AG8" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH8" s="11">
+      <c r="AH8" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI8" s="13">
         <v>8.0</v>
       </c>
-      <c r="AI8" s="11">
+      <c r="AJ8" s="13">
         <v>62.0</v>
       </c>
-      <c r="AJ8" s="11">
+      <c r="AK8" s="13">
         <v>10646.0</v>
       </c>
-      <c r="AK8" s="11">
+      <c r="AL8" s="13">
         <v>665.0</v>
       </c>
-      <c r="AL8" s="11">
+      <c r="AM8" s="13">
         <v>22935.0</v>
       </c>
-      <c r="AM8" s="11">
+      <c r="AN8" s="13">
         <v>280.0</v>
       </c>
-      <c r="AN8" s="11">
+      <c r="AO8" s="13">
         <v>1575.0</v>
       </c>
-      <c r="AO8" s="11">
+      <c r="AP8" s="13">
         <v>7292.0</v>
       </c>
-      <c r="AP8" s="11">
+      <c r="AQ8" s="13">
         <v>16669.0</v>
       </c>
-      <c r="AQ8" s="11">
+      <c r="AR8" s="13">
         <v>829.0</v>
       </c>
-      <c r="AR8" s="11">
+      <c r="AS8" s="13">
         <v>13177.0</v>
       </c>
-      <c r="AS8" s="11">
+      <c r="AT8" s="13">
         <v>844.0</v>
       </c>
-      <c r="AT8" s="11">
+      <c r="AU8" s="13">
         <v>7418.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>62</v>
+      <c r="A9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="9">
+        <v>280541.0</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="10">
+      <c r="D9" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="12">
         <v>3657.0</v>
       </c>
-      <c r="F9" s="10">
+      <c r="G9" s="12">
         <v>8707.0</v>
       </c>
-      <c r="G9" s="11">
+      <c r="H9" s="13">
         <v>4609.0</v>
       </c>
-      <c r="H9" s="11">
+      <c r="I9" s="13">
         <v>4098.0</v>
       </c>
-      <c r="I9" s="11">
+      <c r="J9" s="13">
         <v>334.0</v>
       </c>
-      <c r="J9" s="11">
+      <c r="K9" s="13">
         <v>498.0</v>
       </c>
-      <c r="K9" s="11">
+      <c r="L9" s="13">
         <v>544.0</v>
       </c>
-      <c r="L9" s="11">
+      <c r="M9" s="13">
         <v>556.0</v>
       </c>
-      <c r="M9" s="11">
+      <c r="N9" s="13">
         <v>526.0</v>
       </c>
-      <c r="N9" s="11">
+      <c r="O9" s="13">
         <v>489.0</v>
       </c>
-      <c r="O9" s="11">
+      <c r="P9" s="13">
         <v>532.0</v>
       </c>
-      <c r="P9" s="11">
+      <c r="Q9" s="13">
         <v>619.0</v>
       </c>
-      <c r="Q9" s="11">
+      <c r="R9" s="13">
         <v>739.0</v>
       </c>
-      <c r="R9" s="11">
+      <c r="S9" s="13">
         <v>687.0</v>
       </c>
-      <c r="S9" s="11">
+      <c r="T9" s="13">
         <v>610.0</v>
       </c>
-      <c r="T9" s="11">
+      <c r="U9" s="13">
         <v>486.0</v>
       </c>
-      <c r="U9" s="11">
+      <c r="V9" s="13">
         <v>487.0</v>
       </c>
-      <c r="V9" s="11">
+      <c r="W9" s="13">
         <v>457.0</v>
       </c>
-      <c r="W9" s="11">
+      <c r="X9" s="13">
         <v>428.0</v>
       </c>
-      <c r="X9" s="11">
+      <c r="Y9" s="13">
         <v>306.0</v>
       </c>
-      <c r="Y9" s="11">
+      <c r="Z9" s="13">
         <v>207.0</v>
       </c>
-      <c r="Z9" s="11">
+      <c r="AA9" s="13">
         <v>130.0</v>
       </c>
-      <c r="AA9" s="11">
+      <c r="AB9" s="13">
         <v>57.0</v>
       </c>
-      <c r="AB9" s="11">
+      <c r="AC9" s="13">
         <v>14.0</v>
       </c>
-      <c r="AC9" s="11">
+      <c r="AD9" s="13">
         <v>1.0</v>
       </c>
-      <c r="AD9" s="11">
+      <c r="AE9" s="13">
         <v>3377.0</v>
       </c>
-      <c r="AE9" s="11">
+      <c r="AF9" s="13">
         <v>15.0</v>
       </c>
-      <c r="AF9" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG9" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH9" s="11">
+      <c r="AG9" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH9" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI9" s="13">
         <v>1.0</v>
       </c>
-      <c r="AI9" s="11">
+      <c r="AJ9" s="13">
         <v>20.0</v>
       </c>
-      <c r="AJ9" s="11">
+      <c r="AK9" s="13">
         <v>3086.0</v>
       </c>
-      <c r="AK9" s="11">
+      <c r="AL9" s="13">
         <v>327.0</v>
       </c>
-      <c r="AL9" s="11">
+      <c r="AM9" s="13">
         <v>7162.0</v>
       </c>
-      <c r="AM9" s="11">
+      <c r="AN9" s="13">
         <v>139.0</v>
       </c>
-      <c r="AN9" s="11">
+      <c r="AO9" s="13">
         <v>1406.0</v>
       </c>
-      <c r="AO9" s="11">
+      <c r="AP9" s="13">
         <v>2665.0</v>
       </c>
-      <c r="AP9" s="11">
+      <c r="AQ9" s="13">
         <v>5787.0</v>
       </c>
-      <c r="AQ9" s="11">
+      <c r="AR9" s="13">
         <v>255.0</v>
       </c>
-      <c r="AR9" s="11">
+      <c r="AS9" s="13">
         <v>4455.0</v>
       </c>
-      <c r="AS9" s="11">
+      <c r="AT9" s="13">
         <v>408.0</v>
       </c>
-      <c r="AT9" s="11">
+      <c r="AU9" s="13">
         <v>2587.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>64</v>
+      <c r="A10" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="9">
+        <v>280541.0</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="10">
+      <c r="D10" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="12">
         <v>11030.0</v>
       </c>
-      <c r="F10" s="10">
+      <c r="G10" s="12">
         <v>26720.0</v>
       </c>
-      <c r="G10" s="11">
+      <c r="H10" s="13">
         <v>14017.0</v>
       </c>
-      <c r="H10" s="11">
+      <c r="I10" s="13">
         <v>12703.0</v>
       </c>
-      <c r="I10" s="11">
+      <c r="J10" s="13">
         <v>1210.0</v>
       </c>
-      <c r="J10" s="11">
+      <c r="K10" s="13">
         <v>1609.0</v>
       </c>
-      <c r="K10" s="11">
+      <c r="L10" s="13">
         <v>1728.0</v>
       </c>
-      <c r="L10" s="11">
+      <c r="M10" s="13">
         <v>1811.0</v>
       </c>
-      <c r="M10" s="11">
+      <c r="N10" s="13">
         <v>1699.0</v>
       </c>
-      <c r="N10" s="11">
+      <c r="O10" s="13">
         <v>1726.0</v>
       </c>
-      <c r="O10" s="11">
+      <c r="P10" s="13">
         <v>1876.0</v>
       </c>
-      <c r="P10" s="11">
+      <c r="Q10" s="13">
         <v>1818.0</v>
       </c>
-      <c r="Q10" s="11">
+      <c r="R10" s="13">
         <v>1983.0</v>
       </c>
-      <c r="R10" s="11">
+      <c r="S10" s="13">
         <v>1911.0</v>
       </c>
-      <c r="S10" s="11">
+      <c r="T10" s="13">
         <v>1619.0</v>
       </c>
-      <c r="T10" s="11">
+      <c r="U10" s="13">
         <v>1564.0</v>
       </c>
-      <c r="U10" s="11">
+      <c r="V10" s="13">
         <v>1466.0</v>
       </c>
-      <c r="V10" s="11">
+      <c r="W10" s="13">
         <v>1266.0</v>
       </c>
-      <c r="W10" s="11">
+      <c r="X10" s="13">
         <v>1154.0</v>
       </c>
-      <c r="X10" s="11">
+      <c r="Y10" s="13">
         <v>952.0</v>
       </c>
-      <c r="Y10" s="11">
+      <c r="Z10" s="13">
         <v>628.0</v>
       </c>
-      <c r="Z10" s="11">
+      <c r="AA10" s="13">
         <v>429.0</v>
       </c>
-      <c r="AA10" s="11">
+      <c r="AB10" s="13">
         <v>222.0</v>
       </c>
-      <c r="AB10" s="11">
+      <c r="AC10" s="13">
         <v>43.0</v>
       </c>
-      <c r="AC10" s="11">
+      <c r="AD10" s="13">
         <v>6.0</v>
       </c>
-      <c r="AD10" s="11">
+      <c r="AE10" s="13">
         <v>9904.0</v>
       </c>
-      <c r="AE10" s="11">
+      <c r="AF10" s="13">
         <v>160.0</v>
       </c>
-      <c r="AF10" s="11">
+      <c r="AG10" s="13">
         <v>11.0</v>
       </c>
-      <c r="AG10" s="11">
+      <c r="AH10" s="13">
         <v>13.0</v>
       </c>
-      <c r="AH10" s="11">
+      <c r="AI10" s="13">
         <v>10.0</v>
       </c>
-      <c r="AI10" s="11">
+      <c r="AJ10" s="13">
         <v>88.0</v>
       </c>
-      <c r="AJ10" s="11">
+      <c r="AK10" s="13">
         <v>8971.0</v>
       </c>
-      <c r="AK10" s="11">
+      <c r="AL10" s="13">
         <v>1215.0</v>
       </c>
-      <c r="AL10" s="11">
+      <c r="AM10" s="13">
         <v>20368.0</v>
       </c>
-      <c r="AM10" s="11">
+      <c r="AN10" s="13">
         <v>580.0</v>
       </c>
-      <c r="AN10" s="11">
+      <c r="AO10" s="13">
         <v>5772.0</v>
       </c>
-      <c r="AO10" s="11">
+      <c r="AP10" s="13">
         <v>8290.0</v>
       </c>
-      <c r="AP10" s="11">
+      <c r="AQ10" s="13">
         <v>17336.0</v>
       </c>
-      <c r="AQ10" s="11">
+      <c r="AR10" s="13">
         <v>1094.0</v>
       </c>
-      <c r="AR10" s="11">
+      <c r="AS10" s="13">
         <v>13358.0</v>
       </c>
-      <c r="AS10" s="11">
+      <c r="AT10" s="13">
         <v>1249.0</v>
       </c>
-      <c r="AT10" s="11">
+      <c r="AU10" s="13">
         <v>7923.0</v>
       </c>
     </row>

--- a/DATOS/Datos procesados/Censo 2022 - Vicente López.xlsx
+++ b/DATOS/Datos procesados/Censo 2022 - Vicente López.xlsx
@@ -9,19 +9,16 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="sWGVoQATAyQcF/NeL9cgsMElGKsuIclqakp8gBaj0vY="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="WYlueJLDsH35bKsdmKFy/0YVuNsIKpDx55r0IC22EEk="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="66">
   <si>
     <t>Municipios</t>
-  </si>
-  <si>
-    <t>Total de población</t>
   </si>
   <si>
     <t>Localidades</t>
@@ -296,14 +293,11 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -323,9 +317,6 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="1"/>
@@ -556,14 +547,14 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="61.0"/>
+    <col customWidth="1" min="3" max="3" width="61.0"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -572,1420 +563,1390 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AA1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AD1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AE1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AF1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AG1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AH1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AI1" s="5" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="7" t="s">
+      <c r="AK1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="7" t="s">
+      <c r="AL1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AM1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AN1" s="5" t="s">
         <v>39</v>
       </c>
       <c r="AO1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="7" t="s">
+      <c r="AP1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="7" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="7" t="s">
+      <c r="AR1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="7" t="s">
+      <c r="AS1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="7" t="s">
+      <c r="AT1" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="AU1" s="7" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="B2" s="9">
-        <v>280541.0</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10">
+        <v>6995.0</v>
+      </c>
+      <c r="F2" s="10">
+        <v>16914.0</v>
+      </c>
+      <c r="G2" s="11">
+        <v>8910.0</v>
+      </c>
+      <c r="H2" s="11">
+        <v>8004.0</v>
+      </c>
+      <c r="I2" s="11">
+        <v>681.0</v>
+      </c>
+      <c r="J2" s="11">
+        <v>939.0</v>
+      </c>
+      <c r="K2" s="11">
+        <v>1101.0</v>
+      </c>
+      <c r="L2" s="11">
+        <v>1090.0</v>
+      </c>
+      <c r="M2" s="11">
+        <v>999.0</v>
+      </c>
+      <c r="N2" s="11">
+        <v>865.0</v>
+      </c>
+      <c r="O2" s="11">
+        <v>939.0</v>
+      </c>
+      <c r="P2" s="11">
+        <v>1118.0</v>
+      </c>
+      <c r="Q2" s="11">
+        <v>1364.0</v>
+      </c>
+      <c r="R2" s="11">
+        <v>1391.0</v>
+      </c>
+      <c r="S2" s="11">
+        <v>1137.0</v>
+      </c>
+      <c r="T2" s="11">
+        <v>1019.0</v>
+      </c>
+      <c r="U2" s="11">
+        <v>956.0</v>
+      </c>
+      <c r="V2" s="11">
+        <v>914.0</v>
+      </c>
+      <c r="W2" s="11">
+        <v>838.0</v>
+      </c>
+      <c r="X2" s="11">
+        <v>687.0</v>
+      </c>
+      <c r="Y2" s="11">
+        <v>449.0</v>
+      </c>
+      <c r="Z2" s="11">
+        <v>267.0</v>
+      </c>
+      <c r="AA2" s="11">
+        <v>127.0</v>
+      </c>
+      <c r="AB2" s="11">
+        <v>31.0</v>
+      </c>
+      <c r="AC2" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="AD2" s="11">
+        <v>6509.0</v>
+      </c>
+      <c r="AE2" s="11">
+        <v>26.0</v>
+      </c>
+      <c r="AF2" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="AG2" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="12">
-        <v>6995.0</v>
-      </c>
-      <c r="G2" s="12">
-        <v>16914.0</v>
-      </c>
-      <c r="H2" s="13">
-        <v>8910.0</v>
-      </c>
-      <c r="I2" s="13">
-        <v>8004.0</v>
-      </c>
-      <c r="J2" s="13">
-        <v>681.0</v>
-      </c>
-      <c r="K2" s="13">
-        <v>939.0</v>
-      </c>
-      <c r="L2" s="13">
-        <v>1101.0</v>
-      </c>
-      <c r="M2" s="13">
-        <v>1090.0</v>
-      </c>
-      <c r="N2" s="13">
-        <v>999.0</v>
-      </c>
-      <c r="O2" s="13">
-        <v>865.0</v>
-      </c>
-      <c r="P2" s="13">
-        <v>939.0</v>
-      </c>
-      <c r="Q2" s="13">
-        <v>1118.0</v>
-      </c>
-      <c r="R2" s="13">
-        <v>1364.0</v>
-      </c>
-      <c r="S2" s="13">
-        <v>1391.0</v>
-      </c>
-      <c r="T2" s="13">
-        <v>1137.0</v>
-      </c>
-      <c r="U2" s="13">
-        <v>1019.0</v>
-      </c>
-      <c r="V2" s="13">
-        <v>956.0</v>
-      </c>
-      <c r="W2" s="13">
-        <v>914.0</v>
-      </c>
-      <c r="X2" s="13">
-        <v>838.0</v>
-      </c>
-      <c r="Y2" s="13">
-        <v>687.0</v>
-      </c>
-      <c r="Z2" s="13">
-        <v>449.0</v>
-      </c>
-      <c r="AA2" s="13">
-        <v>267.0</v>
-      </c>
-      <c r="AB2" s="13">
-        <v>127.0</v>
-      </c>
-      <c r="AC2" s="13">
-        <v>31.0</v>
-      </c>
-      <c r="AD2" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AE2" s="13">
-        <v>6509.0</v>
-      </c>
-      <c r="AF2" s="13">
-        <v>26.0</v>
-      </c>
-      <c r="AG2" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="AH2" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI2" s="13">
+      <c r="AH2" s="11">
         <v>1.0</v>
       </c>
-      <c r="AJ2" s="13">
+      <c r="AI2" s="11">
         <v>40.0</v>
       </c>
-      <c r="AK2" s="13">
+      <c r="AJ2" s="11">
         <v>5981.0</v>
       </c>
-      <c r="AL2" s="13">
+      <c r="AK2" s="11">
         <v>597.0</v>
       </c>
-      <c r="AM2" s="13">
+      <c r="AL2" s="11">
         <v>14271.0</v>
       </c>
-      <c r="AN2" s="13">
+      <c r="AM2" s="11">
         <v>227.0</v>
       </c>
-      <c r="AO2" s="13">
+      <c r="AN2" s="11">
         <v>2416.0</v>
       </c>
-      <c r="AP2" s="13">
+      <c r="AO2" s="11">
         <v>5131.0</v>
       </c>
-      <c r="AQ2" s="13">
+      <c r="AP2" s="11">
         <v>11463.0</v>
       </c>
-      <c r="AR2" s="13">
+      <c r="AQ2" s="11">
         <v>320.0</v>
       </c>
-      <c r="AS2" s="13">
+      <c r="AR2" s="11">
         <v>8507.0</v>
       </c>
-      <c r="AT2" s="13">
+      <c r="AS2" s="11">
         <v>722.0</v>
       </c>
-      <c r="AU2" s="13">
+      <c r="AT2" s="11">
         <v>5184.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="9">
-        <v>280541.0</v>
-      </c>
-      <c r="C3" s="14" t="s">
+      <c r="A3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="12">
+      <c r="D3" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="10">
         <v>22270.0</v>
       </c>
-      <c r="G3" s="12">
+      <c r="F3" s="10">
         <v>49536.0</v>
       </c>
-      <c r="H3" s="13">
+      <c r="G3" s="11">
         <v>26765.0</v>
       </c>
-      <c r="I3" s="13">
+      <c r="H3" s="11">
         <v>22771.0</v>
       </c>
-      <c r="J3" s="13">
+      <c r="I3" s="11">
         <v>2083.0</v>
       </c>
-      <c r="K3" s="13">
+      <c r="J3" s="11">
         <v>2563.0</v>
       </c>
-      <c r="L3" s="13">
+      <c r="K3" s="11">
         <v>3041.0</v>
       </c>
-      <c r="M3" s="13">
+      <c r="L3" s="11">
         <v>3155.0</v>
       </c>
-      <c r="N3" s="13">
+      <c r="M3" s="11">
         <v>2895.0</v>
       </c>
-      <c r="O3" s="13">
+      <c r="N3" s="11">
         <v>2741.0</v>
       </c>
-      <c r="P3" s="13">
+      <c r="O3" s="11">
         <v>3087.0</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="P3" s="11">
         <v>3502.0</v>
       </c>
-      <c r="R3" s="13">
+      <c r="Q3" s="11">
         <v>3652.0</v>
       </c>
-      <c r="S3" s="13">
+      <c r="R3" s="11">
         <v>3821.0</v>
       </c>
-      <c r="T3" s="13">
+      <c r="S3" s="11">
         <v>3329.0</v>
       </c>
-      <c r="U3" s="13">
+      <c r="T3" s="11">
         <v>3086.0</v>
       </c>
-      <c r="V3" s="13">
+      <c r="U3" s="11">
         <v>3009.0</v>
       </c>
-      <c r="W3" s="13">
+      <c r="V3" s="11">
         <v>2406.0</v>
       </c>
-      <c r="X3" s="13">
+      <c r="W3" s="11">
         <v>2284.0</v>
       </c>
-      <c r="Y3" s="13">
+      <c r="X3" s="11">
         <v>1974.0</v>
       </c>
-      <c r="Z3" s="13">
+      <c r="Y3" s="11">
         <v>1428.0</v>
       </c>
-      <c r="AA3" s="13">
+      <c r="Z3" s="11">
         <v>919.0</v>
       </c>
-      <c r="AB3" s="13">
+      <c r="AA3" s="11">
         <v>449.0</v>
       </c>
-      <c r="AC3" s="13">
+      <c r="AB3" s="11">
         <v>102.0</v>
       </c>
-      <c r="AD3" s="13">
+      <c r="AC3" s="11">
         <v>10.0</v>
       </c>
-      <c r="AE3" s="13">
+      <c r="AD3" s="11">
         <v>20246.0</v>
       </c>
-      <c r="AF3" s="13">
+      <c r="AE3" s="11">
         <v>100.0</v>
       </c>
-      <c r="AG3" s="13">
+      <c r="AF3" s="11">
         <v>39.0</v>
       </c>
-      <c r="AH3" s="13">
+      <c r="AG3" s="11">
         <v>25.0</v>
       </c>
-      <c r="AI3" s="13">
+      <c r="AH3" s="11">
         <v>22.0</v>
       </c>
-      <c r="AJ3" s="13">
+      <c r="AI3" s="11">
         <v>157.0</v>
       </c>
-      <c r="AK3" s="13">
+      <c r="AJ3" s="11">
         <v>19133.0</v>
       </c>
-      <c r="AL3" s="13">
+      <c r="AK3" s="11">
         <v>1456.0</v>
       </c>
-      <c r="AM3" s="13">
+      <c r="AL3" s="11">
         <v>44666.0</v>
       </c>
-      <c r="AN3" s="13">
+      <c r="AM3" s="11">
         <v>733.0</v>
       </c>
-      <c r="AO3" s="13">
+      <c r="AN3" s="11">
         <v>4137.0</v>
       </c>
-      <c r="AP3" s="13">
+      <c r="AO3" s="11">
         <v>15196.0</v>
       </c>
-      <c r="AQ3" s="13">
+      <c r="AP3" s="11">
         <v>32648.0</v>
       </c>
-      <c r="AR3" s="13">
+      <c r="AQ3" s="11">
         <v>1692.0</v>
       </c>
-      <c r="AS3" s="13">
+      <c r="AR3" s="11">
         <v>25955.0</v>
       </c>
-      <c r="AT3" s="13">
+      <c r="AS3" s="11">
         <v>2311.0</v>
       </c>
-      <c r="AU3" s="13">
+      <c r="AT3" s="11">
         <v>14243.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="9">
-        <v>280541.0</v>
+      <c r="A4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="12">
+      <c r="D4" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="10">
         <v>11524.0</v>
       </c>
-      <c r="G4" s="12">
+      <c r="F4" s="10">
         <v>28227.0</v>
       </c>
-      <c r="H4" s="13">
+      <c r="G4" s="11">
         <v>14713.0</v>
       </c>
-      <c r="I4" s="13">
+      <c r="H4" s="11">
         <v>13514.0</v>
       </c>
-      <c r="J4" s="13">
+      <c r="I4" s="11">
         <v>1268.0</v>
       </c>
-      <c r="K4" s="13">
+      <c r="J4" s="11">
         <v>1889.0</v>
       </c>
-      <c r="L4" s="13">
+      <c r="K4" s="11">
         <v>1992.0</v>
       </c>
-      <c r="M4" s="13">
+      <c r="L4" s="11">
         <v>1937.0</v>
       </c>
-      <c r="N4" s="13">
+      <c r="M4" s="11">
         <v>1792.0</v>
       </c>
-      <c r="O4" s="13">
+      <c r="N4" s="11">
         <v>1731.0</v>
       </c>
-      <c r="P4" s="13">
+      <c r="O4" s="11">
         <v>1970.0</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="P4" s="11">
         <v>2137.0</v>
       </c>
-      <c r="R4" s="13">
+      <c r="Q4" s="11">
         <v>2169.0</v>
       </c>
-      <c r="S4" s="13">
+      <c r="R4" s="11">
         <v>2003.0</v>
       </c>
-      <c r="T4" s="13">
+      <c r="S4" s="11">
         <v>1766.0</v>
       </c>
-      <c r="U4" s="13">
+      <c r="T4" s="11">
         <v>1540.0</v>
       </c>
-      <c r="V4" s="13">
+      <c r="U4" s="11">
         <v>1499.0</v>
       </c>
-      <c r="W4" s="13">
+      <c r="V4" s="11">
         <v>1324.0</v>
       </c>
-      <c r="X4" s="13">
+      <c r="W4" s="11">
         <v>1177.0</v>
       </c>
-      <c r="Y4" s="13">
+      <c r="X4" s="11">
         <v>857.0</v>
       </c>
-      <c r="Z4" s="13">
+      <c r="Y4" s="11">
         <v>589.0</v>
       </c>
-      <c r="AA4" s="13">
+      <c r="Z4" s="11">
         <v>352.0</v>
       </c>
-      <c r="AB4" s="13">
+      <c r="AA4" s="11">
         <v>163.0</v>
       </c>
-      <c r="AC4" s="13">
+      <c r="AB4" s="11">
         <v>61.0</v>
       </c>
-      <c r="AD4" s="13">
+      <c r="AC4" s="11">
         <v>11.0</v>
       </c>
-      <c r="AE4" s="13">
+      <c r="AD4" s="11">
         <v>10484.0</v>
       </c>
-      <c r="AF4" s="13">
+      <c r="AE4" s="11">
         <v>97.0</v>
       </c>
-      <c r="AG4" s="13">
+      <c r="AF4" s="11">
         <v>4.0</v>
       </c>
-      <c r="AH4" s="13">
+      <c r="AG4" s="11">
         <v>11.0</v>
       </c>
-      <c r="AI4" s="13">
+      <c r="AH4" s="11">
         <v>5.0</v>
       </c>
-      <c r="AJ4" s="13">
+      <c r="AI4" s="11">
         <v>70.0</v>
       </c>
-      <c r="AK4" s="13">
+      <c r="AJ4" s="11">
         <v>9387.0</v>
       </c>
-      <c r="AL4" s="13">
+      <c r="AK4" s="11">
         <v>1284.0</v>
       </c>
-      <c r="AM4" s="13">
+      <c r="AL4" s="11">
         <v>20721.0</v>
       </c>
-      <c r="AN4" s="13">
+      <c r="AM4" s="11">
         <v>650.0</v>
       </c>
-      <c r="AO4" s="13">
+      <c r="AN4" s="11">
         <v>6856.0</v>
       </c>
-      <c r="AP4" s="13">
+      <c r="AO4" s="11">
         <v>9021.0</v>
       </c>
-      <c r="AQ4" s="13">
+      <c r="AP4" s="11">
         <v>18445.0</v>
       </c>
-      <c r="AR4" s="13">
+      <c r="AQ4" s="11">
         <v>761.0</v>
       </c>
-      <c r="AS4" s="13">
+      <c r="AR4" s="11">
         <v>14289.0</v>
       </c>
-      <c r="AT4" s="13">
+      <c r="AS4" s="11">
         <v>1237.0</v>
       </c>
-      <c r="AU4" s="13">
+      <c r="AT4" s="11">
         <v>7936.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="9">
-        <v>280541.0</v>
+      <c r="A5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" s="12">
+      <c r="D5" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="10">
         <v>6321.0</v>
       </c>
-      <c r="G5" s="12">
+      <c r="F5" s="10">
         <v>13554.0</v>
       </c>
-      <c r="H5" s="13">
+      <c r="G5" s="11">
         <v>7236.0</v>
       </c>
-      <c r="I5" s="13">
+      <c r="H5" s="11">
         <v>6318.0</v>
       </c>
-      <c r="J5" s="13">
+      <c r="I5" s="11">
         <v>609.0</v>
       </c>
-      <c r="K5" s="13">
+      <c r="J5" s="11">
         <v>710.0</v>
       </c>
-      <c r="L5" s="13">
+      <c r="K5" s="11">
         <v>781.0</v>
       </c>
-      <c r="M5" s="13">
+      <c r="L5" s="11">
         <v>822.0</v>
       </c>
-      <c r="N5" s="13">
+      <c r="M5" s="11">
         <v>781.0</v>
       </c>
-      <c r="O5" s="13">
+      <c r="N5" s="11">
         <v>720.0</v>
       </c>
-      <c r="P5" s="13">
+      <c r="O5" s="11">
         <v>790.0</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="P5" s="11">
         <v>880.0</v>
       </c>
-      <c r="R5" s="13">
+      <c r="Q5" s="11">
         <v>1004.0</v>
       </c>
-      <c r="S5" s="13">
+      <c r="R5" s="11">
         <v>1012.0</v>
       </c>
-      <c r="T5" s="13">
+      <c r="S5" s="11">
         <v>932.0</v>
       </c>
-      <c r="U5" s="13">
+      <c r="T5" s="11">
         <v>797.0</v>
       </c>
-      <c r="V5" s="13">
+      <c r="U5" s="11">
         <v>851.0</v>
       </c>
-      <c r="W5" s="13">
+      <c r="V5" s="11">
         <v>727.0</v>
       </c>
-      <c r="X5" s="13">
+      <c r="W5" s="11">
         <v>732.0</v>
       </c>
-      <c r="Y5" s="13">
+      <c r="X5" s="11">
         <v>574.0</v>
       </c>
-      <c r="Z5" s="13">
+      <c r="Y5" s="11">
         <v>394.0</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="Z5" s="11">
         <v>259.0</v>
       </c>
-      <c r="AB5" s="13">
+      <c r="AA5" s="11">
         <v>140.0</v>
       </c>
-      <c r="AC5" s="13">
+      <c r="AB5" s="11">
         <v>36.0</v>
       </c>
-      <c r="AD5" s="13">
+      <c r="AC5" s="11">
         <v>3.0</v>
       </c>
-      <c r="AE5" s="13">
+      <c r="AD5" s="11">
         <v>5466.0</v>
       </c>
-      <c r="AF5" s="13">
+      <c r="AE5" s="11">
         <v>53.0</v>
       </c>
-      <c r="AG5" s="13">
+      <c r="AF5" s="11">
         <v>7.0</v>
       </c>
-      <c r="AH5" s="13">
+      <c r="AG5" s="11">
         <v>3.0</v>
       </c>
-      <c r="AI5" s="13">
+      <c r="AH5" s="11">
         <v>6.0</v>
       </c>
-      <c r="AJ5" s="13">
+      <c r="AI5" s="11">
         <v>33.0</v>
       </c>
-      <c r="AK5" s="13">
+      <c r="AJ5" s="11">
         <v>5227.0</v>
       </c>
-      <c r="AL5" s="13">
+      <c r="AK5" s="11">
         <v>341.0</v>
       </c>
-      <c r="AM5" s="13">
+      <c r="AL5" s="11">
         <v>12426.0</v>
       </c>
-      <c r="AN5" s="13">
+      <c r="AM5" s="11">
         <v>176.0</v>
       </c>
-      <c r="AO5" s="13">
+      <c r="AN5" s="11">
         <v>952.0</v>
       </c>
-      <c r="AP5" s="13">
+      <c r="AO5" s="11">
         <v>4000.0</v>
       </c>
-      <c r="AQ5" s="13">
+      <c r="AP5" s="11">
         <v>8923.0</v>
       </c>
-      <c r="AR5" s="13">
+      <c r="AQ5" s="11">
         <v>631.0</v>
       </c>
-      <c r="AS5" s="13">
+      <c r="AR5" s="11">
         <v>6897.0</v>
       </c>
-      <c r="AT5" s="13">
+      <c r="AS5" s="11">
         <v>646.0</v>
       </c>
-      <c r="AU5" s="13">
+      <c r="AT5" s="11">
         <v>4077.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="9">
-        <v>280541.0</v>
+      <c r="A6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="12">
+      <c r="D6" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="10">
         <v>14580.0</v>
       </c>
-      <c r="G6" s="12">
+      <c r="F6" s="10">
         <v>34797.0</v>
       </c>
-      <c r="H6" s="13">
+      <c r="G6" s="11">
         <v>18277.0</v>
       </c>
-      <c r="I6" s="13">
+      <c r="H6" s="11">
         <v>16520.0</v>
       </c>
-      <c r="J6" s="13">
+      <c r="I6" s="11">
         <v>1502.0</v>
       </c>
-      <c r="K6" s="13">
+      <c r="J6" s="11">
         <v>2037.0</v>
       </c>
-      <c r="L6" s="13">
+      <c r="K6" s="11">
         <v>2099.0</v>
       </c>
-      <c r="M6" s="13">
+      <c r="L6" s="11">
         <v>2258.0</v>
       </c>
-      <c r="N6" s="13">
+      <c r="M6" s="11">
         <v>2169.0</v>
       </c>
-      <c r="O6" s="13">
+      <c r="N6" s="11">
         <v>2158.0</v>
       </c>
-      <c r="P6" s="13">
+      <c r="O6" s="11">
         <v>2461.0</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="P6" s="11">
         <v>2584.0</v>
       </c>
-      <c r="R6" s="13">
+      <c r="Q6" s="11">
         <v>2800.0</v>
       </c>
-      <c r="S6" s="13">
+      <c r="R6" s="11">
         <v>2539.0</v>
       </c>
-      <c r="T6" s="13">
+      <c r="S6" s="11">
         <v>2346.0</v>
       </c>
-      <c r="U6" s="13">
+      <c r="T6" s="11">
         <v>1963.0</v>
       </c>
-      <c r="V6" s="13">
+      <c r="U6" s="11">
         <v>1877.0</v>
       </c>
-      <c r="W6" s="13">
+      <c r="V6" s="11">
         <v>1705.0</v>
       </c>
-      <c r="X6" s="13">
+      <c r="W6" s="11">
         <v>1490.0</v>
       </c>
-      <c r="Y6" s="13">
+      <c r="X6" s="11">
         <v>1163.0</v>
       </c>
-      <c r="Z6" s="13">
+      <c r="Y6" s="11">
         <v>815.0</v>
       </c>
-      <c r="AA6" s="13">
+      <c r="Z6" s="11">
         <v>542.0</v>
       </c>
-      <c r="AB6" s="13">
+      <c r="AA6" s="11">
         <v>222.0</v>
       </c>
-      <c r="AC6" s="13">
+      <c r="AB6" s="11">
         <v>63.0</v>
       </c>
-      <c r="AD6" s="13">
+      <c r="AC6" s="11">
         <v>4.0</v>
       </c>
-      <c r="AE6" s="13">
+      <c r="AD6" s="11">
         <v>13481.0</v>
       </c>
-      <c r="AF6" s="13">
+      <c r="AE6" s="11">
         <v>45.0</v>
       </c>
-      <c r="AG6" s="13">
+      <c r="AF6" s="11">
         <v>4.0</v>
       </c>
-      <c r="AH6" s="13">
+      <c r="AG6" s="11">
         <v>3.0</v>
       </c>
-      <c r="AI6" s="13">
+      <c r="AH6" s="11">
         <v>12.0</v>
       </c>
-      <c r="AJ6" s="13">
+      <c r="AI6" s="11">
         <v>100.0</v>
       </c>
-      <c r="AK6" s="13">
+      <c r="AJ6" s="11">
         <v>12097.0</v>
       </c>
-      <c r="AL6" s="13">
+      <c r="AK6" s="11">
         <v>1548.0</v>
       </c>
-      <c r="AM6" s="13">
+      <c r="AL6" s="11">
         <v>26894.0</v>
       </c>
-      <c r="AN6" s="13">
+      <c r="AM6" s="11">
         <v>640.0</v>
       </c>
-      <c r="AO6" s="13">
+      <c r="AN6" s="11">
         <v>7263.0</v>
       </c>
-      <c r="AP6" s="13">
+      <c r="AO6" s="11">
         <v>10561.0</v>
       </c>
-      <c r="AQ6" s="13">
+      <c r="AP6" s="11">
         <v>23259.0</v>
       </c>
-      <c r="AR6" s="13">
+      <c r="AQ6" s="11">
         <v>977.0</v>
       </c>
-      <c r="AS6" s="13">
+      <c r="AR6" s="11">
         <v>17970.0</v>
       </c>
-      <c r="AT6" s="13">
+      <c r="AS6" s="11">
         <v>1656.0</v>
       </c>
-      <c r="AU6" s="13">
+      <c r="AT6" s="11">
         <v>9979.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="9">
-        <v>280541.0</v>
+      <c r="A7" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="12">
+      <c r="D7" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="10">
         <v>36530.0</v>
       </c>
-      <c r="G7" s="12">
+      <c r="F7" s="10">
         <v>77296.0</v>
       </c>
-      <c r="H7" s="13">
+      <c r="G7" s="11">
         <v>41612.0</v>
       </c>
-      <c r="I7" s="13">
+      <c r="H7" s="11">
         <v>35684.0</v>
       </c>
-      <c r="J7" s="13">
+      <c r="I7" s="11">
         <v>3189.0</v>
       </c>
-      <c r="K7" s="13">
+      <c r="J7" s="11">
         <v>4075.0</v>
       </c>
-      <c r="L7" s="13">
+      <c r="K7" s="11">
         <v>4323.0</v>
       </c>
-      <c r="M7" s="13">
+      <c r="L7" s="11">
         <v>4756.0</v>
       </c>
-      <c r="N7" s="13">
+      <c r="M7" s="11">
         <v>4384.0</v>
       </c>
-      <c r="O7" s="13">
+      <c r="N7" s="11">
         <v>4234.0</v>
       </c>
-      <c r="P7" s="13">
+      <c r="O7" s="11">
         <v>4857.0</v>
       </c>
-      <c r="Q7" s="13">
+      <c r="P7" s="11">
         <v>5339.0</v>
       </c>
-      <c r="R7" s="13">
+      <c r="Q7" s="11">
         <v>5690.0</v>
       </c>
-      <c r="S7" s="13">
+      <c r="R7" s="11">
         <v>5942.0</v>
       </c>
-      <c r="T7" s="13">
+      <c r="S7" s="11">
         <v>5183.0</v>
       </c>
-      <c r="U7" s="13">
+      <c r="T7" s="11">
         <v>4895.0</v>
       </c>
-      <c r="V7" s="13">
+      <c r="U7" s="11">
         <v>4784.0</v>
       </c>
-      <c r="W7" s="13">
+      <c r="V7" s="11">
         <v>4171.0</v>
       </c>
-      <c r="X7" s="13">
+      <c r="W7" s="11">
         <v>3954.0</v>
       </c>
-      <c r="Y7" s="13">
+      <c r="X7" s="11">
         <v>3132.0</v>
       </c>
-      <c r="Z7" s="13">
+      <c r="Y7" s="11">
         <v>2118.0</v>
       </c>
-      <c r="AA7" s="13">
+      <c r="Z7" s="11">
         <v>1308.0</v>
       </c>
-      <c r="AB7" s="13">
+      <c r="AA7" s="11">
         <v>701.0</v>
       </c>
-      <c r="AC7" s="13">
+      <c r="AB7" s="11">
         <v>240.0</v>
       </c>
-      <c r="AD7" s="13">
+      <c r="AC7" s="11">
         <v>21.0</v>
       </c>
-      <c r="AE7" s="13">
+      <c r="AD7" s="11">
         <v>32425.0</v>
       </c>
-      <c r="AF7" s="13">
+      <c r="AE7" s="11">
         <v>128.0</v>
       </c>
-      <c r="AG7" s="13">
+      <c r="AF7" s="11">
         <v>19.0</v>
       </c>
-      <c r="AH7" s="13">
+      <c r="AG7" s="11">
         <v>9.0</v>
       </c>
-      <c r="AI7" s="13">
+      <c r="AH7" s="11">
         <v>22.0</v>
       </c>
-      <c r="AJ7" s="13">
+      <c r="AI7" s="11">
         <v>179.0</v>
       </c>
-      <c r="AK7" s="13">
+      <c r="AJ7" s="11">
         <v>30431.0</v>
       </c>
-      <c r="AL7" s="13">
+      <c r="AK7" s="11">
         <v>2351.0</v>
       </c>
-      <c r="AM7" s="13">
+      <c r="AL7" s="11">
         <v>68629.0</v>
       </c>
-      <c r="AN7" s="13">
+      <c r="AM7" s="11">
         <v>1068.0</v>
       </c>
-      <c r="AO7" s="13">
+      <c r="AN7" s="11">
         <v>7599.0</v>
       </c>
-      <c r="AP7" s="13">
+      <c r="AO7" s="11">
         <v>22946.0</v>
       </c>
-      <c r="AQ7" s="13">
+      <c r="AP7" s="11">
         <v>52574.0</v>
       </c>
-      <c r="AR7" s="13">
+      <c r="AQ7" s="11">
         <v>1776.0</v>
       </c>
-      <c r="AS7" s="13">
+      <c r="AR7" s="11">
         <v>40877.0</v>
       </c>
-      <c r="AT7" s="13">
+      <c r="AS7" s="11">
         <v>2988.0</v>
       </c>
-      <c r="AU7" s="13">
+      <c r="AT7" s="11">
         <v>22731.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="9">
-        <v>280541.0</v>
+      <c r="A8" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="10">
+        <v>12830.0</v>
+      </c>
+      <c r="F8" s="10">
+        <v>24790.0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>13371.0</v>
+      </c>
+      <c r="H8" s="11">
+        <v>11419.0</v>
+      </c>
+      <c r="I8" s="11">
+        <v>1080.0</v>
+      </c>
+      <c r="J8" s="11">
+        <v>1188.0</v>
+      </c>
+      <c r="K8" s="11">
+        <v>1363.0</v>
+      </c>
+      <c r="L8" s="11">
+        <v>1361.0</v>
+      </c>
+      <c r="M8" s="11">
+        <v>1340.0</v>
+      </c>
+      <c r="N8" s="11">
+        <v>1506.0</v>
+      </c>
+      <c r="O8" s="11">
+        <v>1704.0</v>
+      </c>
+      <c r="P8" s="11">
+        <v>1818.0</v>
+      </c>
+      <c r="Q8" s="11">
+        <v>1753.0</v>
+      </c>
+      <c r="R8" s="11">
+        <v>1740.0</v>
+      </c>
+      <c r="S8" s="11">
+        <v>1616.0</v>
+      </c>
+      <c r="T8" s="11">
+        <v>1537.0</v>
+      </c>
+      <c r="U8" s="11">
+        <v>1454.0</v>
+      </c>
+      <c r="V8" s="11">
+        <v>1306.0</v>
+      </c>
+      <c r="W8" s="11">
+        <v>1336.0</v>
+      </c>
+      <c r="X8" s="11">
+        <v>1154.0</v>
+      </c>
+      <c r="Y8" s="11">
+        <v>780.0</v>
+      </c>
+      <c r="Z8" s="11">
+        <v>456.0</v>
+      </c>
+      <c r="AA8" s="11">
+        <v>232.0</v>
+      </c>
+      <c r="AB8" s="11">
+        <v>56.0</v>
+      </c>
+      <c r="AC8" s="11">
+        <v>10.0</v>
+      </c>
+      <c r="AD8" s="11">
+        <v>11192.0</v>
+      </c>
+      <c r="AE8" s="11">
+        <v>42.0</v>
+      </c>
+      <c r="AF8" s="11">
+        <v>7.0</v>
+      </c>
+      <c r="AG8" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="12">
-        <v>12830.0</v>
-      </c>
-      <c r="G8" s="12">
-        <v>24790.0</v>
-      </c>
-      <c r="H8" s="13">
-        <v>13371.0</v>
-      </c>
-      <c r="I8" s="13">
-        <v>11419.0</v>
-      </c>
-      <c r="J8" s="13">
-        <v>1080.0</v>
-      </c>
-      <c r="K8" s="13">
-        <v>1188.0</v>
-      </c>
-      <c r="L8" s="13">
-        <v>1363.0</v>
-      </c>
-      <c r="M8" s="13">
-        <v>1361.0</v>
-      </c>
-      <c r="N8" s="13">
-        <v>1340.0</v>
-      </c>
-      <c r="O8" s="13">
-        <v>1506.0</v>
-      </c>
-      <c r="P8" s="13">
-        <v>1704.0</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>1818.0</v>
-      </c>
-      <c r="R8" s="13">
-        <v>1753.0</v>
-      </c>
-      <c r="S8" s="13">
-        <v>1740.0</v>
-      </c>
-      <c r="T8" s="13">
-        <v>1616.0</v>
-      </c>
-      <c r="U8" s="13">
-        <v>1537.0</v>
-      </c>
-      <c r="V8" s="13">
-        <v>1454.0</v>
-      </c>
-      <c r="W8" s="13">
-        <v>1306.0</v>
-      </c>
-      <c r="X8" s="13">
-        <v>1336.0</v>
-      </c>
-      <c r="Y8" s="13">
-        <v>1154.0</v>
-      </c>
-      <c r="Z8" s="13">
-        <v>780.0</v>
-      </c>
-      <c r="AA8" s="13">
-        <v>456.0</v>
-      </c>
-      <c r="AB8" s="13">
-        <v>232.0</v>
-      </c>
-      <c r="AC8" s="13">
-        <v>56.0</v>
-      </c>
-      <c r="AD8" s="13">
-        <v>10.0</v>
-      </c>
-      <c r="AE8" s="13">
-        <v>11192.0</v>
-      </c>
-      <c r="AF8" s="13">
-        <v>42.0</v>
-      </c>
-      <c r="AG8" s="13">
-        <v>7.0</v>
-      </c>
-      <c r="AH8" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI8" s="13">
+      <c r="AH8" s="11">
         <v>8.0</v>
       </c>
-      <c r="AJ8" s="13">
+      <c r="AI8" s="11">
         <v>62.0</v>
       </c>
-      <c r="AK8" s="13">
+      <c r="AJ8" s="11">
         <v>10646.0</v>
       </c>
-      <c r="AL8" s="13">
+      <c r="AK8" s="11">
         <v>665.0</v>
       </c>
-      <c r="AM8" s="13">
+      <c r="AL8" s="11">
         <v>22935.0</v>
       </c>
-      <c r="AN8" s="13">
+      <c r="AM8" s="11">
         <v>280.0</v>
       </c>
-      <c r="AO8" s="13">
+      <c r="AN8" s="11">
         <v>1575.0</v>
       </c>
-      <c r="AP8" s="13">
+      <c r="AO8" s="11">
         <v>7292.0</v>
       </c>
-      <c r="AQ8" s="13">
+      <c r="AP8" s="11">
         <v>16669.0</v>
       </c>
-      <c r="AR8" s="13">
+      <c r="AQ8" s="11">
         <v>829.0</v>
       </c>
-      <c r="AS8" s="13">
+      <c r="AR8" s="11">
         <v>13177.0</v>
       </c>
-      <c r="AT8" s="13">
+      <c r="AS8" s="11">
         <v>844.0</v>
       </c>
-      <c r="AU8" s="13">
+      <c r="AT8" s="11">
         <v>7418.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="9">
-        <v>280541.0</v>
+      <c r="A9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="15" t="s">
+      <c r="D9" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="10">
+        <v>3657.0</v>
+      </c>
+      <c r="F9" s="10">
+        <v>8707.0</v>
+      </c>
+      <c r="G9" s="11">
+        <v>4609.0</v>
+      </c>
+      <c r="H9" s="11">
+        <v>4098.0</v>
+      </c>
+      <c r="I9" s="11">
+        <v>334.0</v>
+      </c>
+      <c r="J9" s="11">
+        <v>498.0</v>
+      </c>
+      <c r="K9" s="11">
+        <v>544.0</v>
+      </c>
+      <c r="L9" s="11">
+        <v>556.0</v>
+      </c>
+      <c r="M9" s="11">
+        <v>526.0</v>
+      </c>
+      <c r="N9" s="11">
+        <v>489.0</v>
+      </c>
+      <c r="O9" s="11">
+        <v>532.0</v>
+      </c>
+      <c r="P9" s="11">
+        <v>619.0</v>
+      </c>
+      <c r="Q9" s="11">
+        <v>739.0</v>
+      </c>
+      <c r="R9" s="11">
+        <v>687.0</v>
+      </c>
+      <c r="S9" s="11">
+        <v>610.0</v>
+      </c>
+      <c r="T9" s="11">
+        <v>486.0</v>
+      </c>
+      <c r="U9" s="11">
+        <v>487.0</v>
+      </c>
+      <c r="V9" s="11">
+        <v>457.0</v>
+      </c>
+      <c r="W9" s="11">
+        <v>428.0</v>
+      </c>
+      <c r="X9" s="11">
+        <v>306.0</v>
+      </c>
+      <c r="Y9" s="11">
+        <v>207.0</v>
+      </c>
+      <c r="Z9" s="11">
+        <v>130.0</v>
+      </c>
+      <c r="AA9" s="11">
+        <v>57.0</v>
+      </c>
+      <c r="AB9" s="11">
+        <v>14.0</v>
+      </c>
+      <c r="AC9" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="AD9" s="11">
+        <v>3377.0</v>
+      </c>
+      <c r="AE9" s="11">
+        <v>15.0</v>
+      </c>
+      <c r="AF9" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="12">
-        <v>3657.0</v>
-      </c>
-      <c r="G9" s="12">
-        <v>8707.0</v>
-      </c>
-      <c r="H9" s="13">
-        <v>4609.0</v>
-      </c>
-      <c r="I9" s="13">
-        <v>4098.0</v>
-      </c>
-      <c r="J9" s="13">
-        <v>334.0</v>
-      </c>
-      <c r="K9" s="13">
-        <v>498.0</v>
-      </c>
-      <c r="L9" s="13">
-        <v>544.0</v>
-      </c>
-      <c r="M9" s="13">
-        <v>556.0</v>
-      </c>
-      <c r="N9" s="13">
-        <v>526.0</v>
-      </c>
-      <c r="O9" s="13">
-        <v>489.0</v>
-      </c>
-      <c r="P9" s="13">
-        <v>532.0</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>619.0</v>
-      </c>
-      <c r="R9" s="13">
-        <v>739.0</v>
-      </c>
-      <c r="S9" s="13">
-        <v>687.0</v>
-      </c>
-      <c r="T9" s="13">
-        <v>610.0</v>
-      </c>
-      <c r="U9" s="13">
-        <v>486.0</v>
-      </c>
-      <c r="V9" s="13">
-        <v>487.0</v>
-      </c>
-      <c r="W9" s="13">
-        <v>457.0</v>
-      </c>
-      <c r="X9" s="13">
-        <v>428.0</v>
-      </c>
-      <c r="Y9" s="13">
-        <v>306.0</v>
-      </c>
-      <c r="Z9" s="13">
-        <v>207.0</v>
-      </c>
-      <c r="AA9" s="13">
-        <v>130.0</v>
-      </c>
-      <c r="AB9" s="13">
-        <v>57.0</v>
-      </c>
-      <c r="AC9" s="13">
-        <v>14.0</v>
-      </c>
-      <c r="AD9" s="13">
+      <c r="AG9" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH9" s="11">
         <v>1.0</v>
       </c>
-      <c r="AE9" s="13">
-        <v>3377.0</v>
-      </c>
-      <c r="AF9" s="13">
-        <v>15.0</v>
-      </c>
-      <c r="AG9" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH9" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI9" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="AJ9" s="13">
+      <c r="AI9" s="11">
         <v>20.0</v>
       </c>
-      <c r="AK9" s="13">
+      <c r="AJ9" s="11">
         <v>3086.0</v>
       </c>
-      <c r="AL9" s="13">
+      <c r="AK9" s="11">
         <v>327.0</v>
       </c>
-      <c r="AM9" s="13">
+      <c r="AL9" s="11">
         <v>7162.0</v>
       </c>
-      <c r="AN9" s="13">
+      <c r="AM9" s="11">
         <v>139.0</v>
       </c>
-      <c r="AO9" s="13">
+      <c r="AN9" s="11">
         <v>1406.0</v>
       </c>
-      <c r="AP9" s="13">
+      <c r="AO9" s="11">
         <v>2665.0</v>
       </c>
-      <c r="AQ9" s="13">
+      <c r="AP9" s="11">
         <v>5787.0</v>
       </c>
-      <c r="AR9" s="13">
+      <c r="AQ9" s="11">
         <v>255.0</v>
       </c>
-      <c r="AS9" s="13">
+      <c r="AR9" s="11">
         <v>4455.0</v>
       </c>
-      <c r="AT9" s="13">
+      <c r="AS9" s="11">
         <v>408.0</v>
       </c>
-      <c r="AU9" s="13">
+      <c r="AT9" s="11">
         <v>2587.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="9">
-        <v>280541.0</v>
+      <c r="A10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="12">
+      <c r="D10" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="10">
         <v>11030.0</v>
       </c>
-      <c r="G10" s="12">
+      <c r="F10" s="10">
         <v>26720.0</v>
       </c>
-      <c r="H10" s="13">
+      <c r="G10" s="11">
         <v>14017.0</v>
       </c>
-      <c r="I10" s="13">
+      <c r="H10" s="11">
         <v>12703.0</v>
       </c>
-      <c r="J10" s="13">
+      <c r="I10" s="11">
         <v>1210.0</v>
       </c>
-      <c r="K10" s="13">
+      <c r="J10" s="11">
         <v>1609.0</v>
       </c>
-      <c r="L10" s="13">
+      <c r="K10" s="11">
         <v>1728.0</v>
       </c>
-      <c r="M10" s="13">
+      <c r="L10" s="11">
         <v>1811.0</v>
       </c>
-      <c r="N10" s="13">
+      <c r="M10" s="11">
         <v>1699.0</v>
       </c>
-      <c r="O10" s="13">
+      <c r="N10" s="11">
         <v>1726.0</v>
       </c>
-      <c r="P10" s="13">
+      <c r="O10" s="11">
         <v>1876.0</v>
       </c>
-      <c r="Q10" s="13">
+      <c r="P10" s="11">
         <v>1818.0</v>
       </c>
-      <c r="R10" s="13">
+      <c r="Q10" s="11">
         <v>1983.0</v>
       </c>
-      <c r="S10" s="13">
+      <c r="R10" s="11">
         <v>1911.0</v>
       </c>
-      <c r="T10" s="13">
+      <c r="S10" s="11">
         <v>1619.0</v>
       </c>
-      <c r="U10" s="13">
+      <c r="T10" s="11">
         <v>1564.0</v>
       </c>
-      <c r="V10" s="13">
+      <c r="U10" s="11">
         <v>1466.0</v>
       </c>
-      <c r="W10" s="13">
+      <c r="V10" s="11">
         <v>1266.0</v>
       </c>
-      <c r="X10" s="13">
+      <c r="W10" s="11">
         <v>1154.0</v>
       </c>
-      <c r="Y10" s="13">
+      <c r="X10" s="11">
         <v>952.0</v>
       </c>
-      <c r="Z10" s="13">
+      <c r="Y10" s="11">
         <v>628.0</v>
       </c>
-      <c r="AA10" s="13">
+      <c r="Z10" s="11">
         <v>429.0</v>
       </c>
-      <c r="AB10" s="13">
+      <c r="AA10" s="11">
         <v>222.0</v>
       </c>
-      <c r="AC10" s="13">
+      <c r="AB10" s="11">
         <v>43.0</v>
       </c>
-      <c r="AD10" s="13">
+      <c r="AC10" s="11">
         <v>6.0</v>
       </c>
-      <c r="AE10" s="13">
+      <c r="AD10" s="11">
         <v>9904.0</v>
       </c>
-      <c r="AF10" s="13">
+      <c r="AE10" s="11">
         <v>160.0</v>
       </c>
-      <c r="AG10" s="13">
+      <c r="AF10" s="11">
         <v>11.0</v>
       </c>
-      <c r="AH10" s="13">
+      <c r="AG10" s="11">
         <v>13.0</v>
       </c>
-      <c r="AI10" s="13">
+      <c r="AH10" s="11">
         <v>10.0</v>
       </c>
-      <c r="AJ10" s="13">
+      <c r="AI10" s="11">
         <v>88.0</v>
       </c>
-      <c r="AK10" s="13">
+      <c r="AJ10" s="11">
         <v>8971.0</v>
       </c>
-      <c r="AL10" s="13">
+      <c r="AK10" s="11">
         <v>1215.0</v>
       </c>
-      <c r="AM10" s="13">
+      <c r="AL10" s="11">
         <v>20368.0</v>
       </c>
-      <c r="AN10" s="13">
+      <c r="AM10" s="11">
         <v>580.0</v>
       </c>
-      <c r="AO10" s="13">
+      <c r="AN10" s="11">
         <v>5772.0</v>
       </c>
-      <c r="AP10" s="13">
+      <c r="AO10" s="11">
         <v>8290.0</v>
       </c>
-      <c r="AQ10" s="13">
+      <c r="AP10" s="11">
         <v>17336.0</v>
       </c>
-      <c r="AR10" s="13">
+      <c r="AQ10" s="11">
         <v>1094.0</v>
       </c>
-      <c r="AS10" s="13">
+      <c r="AR10" s="11">
         <v>13358.0</v>
       </c>
-      <c r="AT10" s="13">
+      <c r="AS10" s="11">
         <v>1249.0</v>
       </c>
-      <c r="AU10" s="13">
+      <c r="AT10" s="11">
         <v>7923.0</v>
       </c>
     </row>

--- a/DATOS/Datos procesados/Censo 2022 - Vicente López.xlsx
+++ b/DATOS/Datos procesados/Censo 2022 - Vicente López.xlsx
@@ -9,16 +9,19 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="WYlueJLDsH35bKsdmKFy/0YVuNsIKpDx55r0IC22EEk="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="sWGVoQATAyQcF/NeL9cgsMElGKsuIclqakp8gBaj0vY="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="67">
   <si>
     <t>Municipios</t>
+  </si>
+  <si>
+    <t>Total poblacional</t>
   </si>
   <si>
     <t>Localidades</t>
@@ -257,7 +260,6 @@
       <sz val="8.0"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8.0"/>
@@ -293,15 +295,15 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
@@ -312,11 +314,8 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="1"/>
@@ -327,9 +326,6 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" wrapText="1"/>
@@ -547,14 +543,14 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="61.0"/>
+    <col customWidth="1" min="4" max="4" width="61.0"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -563,19 +559,19 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
@@ -635,10 +631,10 @@
       <c r="AB1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="5" t="s">
@@ -656,10 +652,10 @@
       <c r="AI1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AK1" s="5" t="s">
         <v>36</v>
       </c>
       <c r="AL1" s="5" t="s">
@@ -671,1282 +667,1312 @@
       <c r="AN1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AO1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AP1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AQ1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AR1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AS1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AT1" s="5" t="s">
         <v>45</v>
+      </c>
+      <c r="AU1" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="6">
+        <v>280541.0</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="9">
         <v>6995.0</v>
       </c>
-      <c r="F2" s="10">
+      <c r="G2" s="9">
         <v>16914.0</v>
       </c>
-      <c r="G2" s="11">
+      <c r="H2" s="10">
         <v>8910.0</v>
       </c>
-      <c r="H2" s="11">
+      <c r="I2" s="10">
         <v>8004.0</v>
       </c>
-      <c r="I2" s="11">
+      <c r="J2" s="10">
         <v>681.0</v>
       </c>
-      <c r="J2" s="11">
+      <c r="K2" s="10">
         <v>939.0</v>
       </c>
-      <c r="K2" s="11">
+      <c r="L2" s="10">
         <v>1101.0</v>
       </c>
-      <c r="L2" s="11">
+      <c r="M2" s="10">
         <v>1090.0</v>
       </c>
-      <c r="M2" s="11">
+      <c r="N2" s="10">
         <v>999.0</v>
       </c>
-      <c r="N2" s="11">
+      <c r="O2" s="10">
         <v>865.0</v>
       </c>
-      <c r="O2" s="11">
+      <c r="P2" s="10">
         <v>939.0</v>
       </c>
-      <c r="P2" s="11">
+      <c r="Q2" s="10">
         <v>1118.0</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="R2" s="10">
         <v>1364.0</v>
       </c>
-      <c r="R2" s="11">
+      <c r="S2" s="10">
         <v>1391.0</v>
       </c>
-      <c r="S2" s="11">
+      <c r="T2" s="10">
         <v>1137.0</v>
       </c>
-      <c r="T2" s="11">
+      <c r="U2" s="10">
         <v>1019.0</v>
       </c>
-      <c r="U2" s="11">
+      <c r="V2" s="10">
         <v>956.0</v>
       </c>
-      <c r="V2" s="11">
+      <c r="W2" s="10">
         <v>914.0</v>
       </c>
-      <c r="W2" s="11">
+      <c r="X2" s="10">
         <v>838.0</v>
       </c>
-      <c r="X2" s="11">
+      <c r="Y2" s="10">
         <v>687.0</v>
       </c>
-      <c r="Y2" s="11">
+      <c r="Z2" s="10">
         <v>449.0</v>
       </c>
-      <c r="Z2" s="11">
+      <c r="AA2" s="10">
         <v>267.0</v>
       </c>
-      <c r="AA2" s="11">
+      <c r="AB2" s="10">
         <v>127.0</v>
       </c>
-      <c r="AB2" s="11">
+      <c r="AC2" s="10">
         <v>31.0</v>
       </c>
-      <c r="AC2" s="11">
+      <c r="AD2" s="10">
         <v>2.0</v>
       </c>
-      <c r="AD2" s="11">
+      <c r="AE2" s="10">
         <v>6509.0</v>
       </c>
-      <c r="AE2" s="11">
+      <c r="AF2" s="10">
         <v>26.0</v>
       </c>
-      <c r="AF2" s="11">
+      <c r="AG2" s="10">
         <v>2.0</v>
       </c>
-      <c r="AG2" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH2" s="11">
+      <c r="AH2" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI2" s="10">
         <v>1.0</v>
       </c>
-      <c r="AI2" s="11">
+      <c r="AJ2" s="10">
         <v>40.0</v>
       </c>
-      <c r="AJ2" s="11">
+      <c r="AK2" s="10">
         <v>5981.0</v>
       </c>
-      <c r="AK2" s="11">
+      <c r="AL2" s="10">
         <v>597.0</v>
       </c>
-      <c r="AL2" s="11">
+      <c r="AM2" s="10">
         <v>14271.0</v>
       </c>
-      <c r="AM2" s="11">
+      <c r="AN2" s="10">
         <v>227.0</v>
       </c>
-      <c r="AN2" s="11">
+      <c r="AO2" s="10">
         <v>2416.0</v>
       </c>
-      <c r="AO2" s="11">
+      <c r="AP2" s="10">
         <v>5131.0</v>
       </c>
-      <c r="AP2" s="11">
+      <c r="AQ2" s="10">
         <v>11463.0</v>
       </c>
-      <c r="AQ2" s="11">
+      <c r="AR2" s="10">
         <v>320.0</v>
       </c>
-      <c r="AR2" s="11">
+      <c r="AS2" s="10">
         <v>8507.0</v>
       </c>
-      <c r="AS2" s="11">
+      <c r="AT2" s="10">
         <v>722.0</v>
       </c>
-      <c r="AT2" s="11">
+      <c r="AU2" s="10">
         <v>5184.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="A3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="6">
+        <v>280541.0</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="10">
+      <c r="D3" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="9">
         <v>22270.0</v>
       </c>
-      <c r="F3" s="10">
+      <c r="G3" s="9">
         <v>49536.0</v>
       </c>
-      <c r="G3" s="11">
+      <c r="H3" s="10">
         <v>26765.0</v>
       </c>
-      <c r="H3" s="11">
+      <c r="I3" s="10">
         <v>22771.0</v>
       </c>
-      <c r="I3" s="11">
+      <c r="J3" s="10">
         <v>2083.0</v>
       </c>
-      <c r="J3" s="11">
+      <c r="K3" s="10">
         <v>2563.0</v>
       </c>
-      <c r="K3" s="11">
+      <c r="L3" s="10">
         <v>3041.0</v>
       </c>
-      <c r="L3" s="11">
+      <c r="M3" s="10">
         <v>3155.0</v>
       </c>
-      <c r="M3" s="11">
+      <c r="N3" s="10">
         <v>2895.0</v>
       </c>
-      <c r="N3" s="11">
+      <c r="O3" s="10">
         <v>2741.0</v>
       </c>
-      <c r="O3" s="11">
+      <c r="P3" s="10">
         <v>3087.0</v>
       </c>
-      <c r="P3" s="11">
+      <c r="Q3" s="10">
         <v>3502.0</v>
       </c>
-      <c r="Q3" s="11">
+      <c r="R3" s="10">
         <v>3652.0</v>
       </c>
-      <c r="R3" s="11">
+      <c r="S3" s="10">
         <v>3821.0</v>
       </c>
-      <c r="S3" s="11">
+      <c r="T3" s="10">
         <v>3329.0</v>
       </c>
-      <c r="T3" s="11">
+      <c r="U3" s="10">
         <v>3086.0</v>
       </c>
-      <c r="U3" s="11">
+      <c r="V3" s="10">
         <v>3009.0</v>
       </c>
-      <c r="V3" s="11">
+      <c r="W3" s="10">
         <v>2406.0</v>
       </c>
-      <c r="W3" s="11">
+      <c r="X3" s="10">
         <v>2284.0</v>
       </c>
-      <c r="X3" s="11">
+      <c r="Y3" s="10">
         <v>1974.0</v>
       </c>
-      <c r="Y3" s="11">
+      <c r="Z3" s="10">
         <v>1428.0</v>
       </c>
-      <c r="Z3" s="11">
+      <c r="AA3" s="10">
         <v>919.0</v>
       </c>
-      <c r="AA3" s="11">
+      <c r="AB3" s="10">
         <v>449.0</v>
       </c>
-      <c r="AB3" s="11">
+      <c r="AC3" s="10">
         <v>102.0</v>
       </c>
-      <c r="AC3" s="11">
+      <c r="AD3" s="10">
         <v>10.0</v>
       </c>
-      <c r="AD3" s="11">
+      <c r="AE3" s="10">
         <v>20246.0</v>
       </c>
-      <c r="AE3" s="11">
+      <c r="AF3" s="10">
         <v>100.0</v>
       </c>
-      <c r="AF3" s="11">
+      <c r="AG3" s="10">
         <v>39.0</v>
       </c>
-      <c r="AG3" s="11">
+      <c r="AH3" s="10">
         <v>25.0</v>
       </c>
-      <c r="AH3" s="11">
+      <c r="AI3" s="10">
         <v>22.0</v>
       </c>
-      <c r="AI3" s="11">
+      <c r="AJ3" s="10">
         <v>157.0</v>
       </c>
-      <c r="AJ3" s="11">
+      <c r="AK3" s="10">
         <v>19133.0</v>
       </c>
-      <c r="AK3" s="11">
+      <c r="AL3" s="10">
         <v>1456.0</v>
       </c>
-      <c r="AL3" s="11">
+      <c r="AM3" s="10">
         <v>44666.0</v>
       </c>
-      <c r="AM3" s="11">
+      <c r="AN3" s="10">
         <v>733.0</v>
       </c>
-      <c r="AN3" s="11">
+      <c r="AO3" s="10">
         <v>4137.0</v>
       </c>
-      <c r="AO3" s="11">
+      <c r="AP3" s="10">
         <v>15196.0</v>
       </c>
-      <c r="AP3" s="11">
+      <c r="AQ3" s="10">
         <v>32648.0</v>
       </c>
-      <c r="AQ3" s="11">
+      <c r="AR3" s="10">
         <v>1692.0</v>
       </c>
-      <c r="AR3" s="11">
+      <c r="AS3" s="10">
         <v>25955.0</v>
       </c>
-      <c r="AS3" s="11">
+      <c r="AT3" s="10">
         <v>2311.0</v>
       </c>
-      <c r="AT3" s="11">
+      <c r="AU3" s="10">
         <v>14243.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="A4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="6">
+        <v>280541.0</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="10">
+      <c r="D4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="9">
         <v>11524.0</v>
       </c>
-      <c r="F4" s="10">
+      <c r="G4" s="9">
         <v>28227.0</v>
       </c>
-      <c r="G4" s="11">
+      <c r="H4" s="10">
         <v>14713.0</v>
       </c>
-      <c r="H4" s="11">
+      <c r="I4" s="10">
         <v>13514.0</v>
       </c>
-      <c r="I4" s="11">
+      <c r="J4" s="10">
         <v>1268.0</v>
       </c>
-      <c r="J4" s="11">
+      <c r="K4" s="10">
         <v>1889.0</v>
       </c>
-      <c r="K4" s="11">
+      <c r="L4" s="10">
         <v>1992.0</v>
       </c>
-      <c r="L4" s="11">
+      <c r="M4" s="10">
         <v>1937.0</v>
       </c>
-      <c r="M4" s="11">
+      <c r="N4" s="10">
         <v>1792.0</v>
       </c>
-      <c r="N4" s="11">
+      <c r="O4" s="10">
         <v>1731.0</v>
       </c>
-      <c r="O4" s="11">
+      <c r="P4" s="10">
         <v>1970.0</v>
       </c>
-      <c r="P4" s="11">
+      <c r="Q4" s="10">
         <v>2137.0</v>
       </c>
-      <c r="Q4" s="11">
+      <c r="R4" s="10">
         <v>2169.0</v>
       </c>
-      <c r="R4" s="11">
+      <c r="S4" s="10">
         <v>2003.0</v>
       </c>
-      <c r="S4" s="11">
+      <c r="T4" s="10">
         <v>1766.0</v>
       </c>
-      <c r="T4" s="11">
+      <c r="U4" s="10">
         <v>1540.0</v>
       </c>
-      <c r="U4" s="11">
+      <c r="V4" s="10">
         <v>1499.0</v>
       </c>
-      <c r="V4" s="11">
+      <c r="W4" s="10">
         <v>1324.0</v>
       </c>
-      <c r="W4" s="11">
+      <c r="X4" s="10">
         <v>1177.0</v>
       </c>
-      <c r="X4" s="11">
+      <c r="Y4" s="10">
         <v>857.0</v>
       </c>
-      <c r="Y4" s="11">
+      <c r="Z4" s="10">
         <v>589.0</v>
       </c>
-      <c r="Z4" s="11">
+      <c r="AA4" s="10">
         <v>352.0</v>
       </c>
-      <c r="AA4" s="11">
+      <c r="AB4" s="10">
         <v>163.0</v>
       </c>
-      <c r="AB4" s="11">
+      <c r="AC4" s="10">
         <v>61.0</v>
       </c>
-      <c r="AC4" s="11">
+      <c r="AD4" s="10">
         <v>11.0</v>
       </c>
-      <c r="AD4" s="11">
+      <c r="AE4" s="10">
         <v>10484.0</v>
       </c>
-      <c r="AE4" s="11">
+      <c r="AF4" s="10">
         <v>97.0</v>
       </c>
-      <c r="AF4" s="11">
+      <c r="AG4" s="10">
         <v>4.0</v>
       </c>
-      <c r="AG4" s="11">
+      <c r="AH4" s="10">
         <v>11.0</v>
       </c>
-      <c r="AH4" s="11">
+      <c r="AI4" s="10">
         <v>5.0</v>
       </c>
-      <c r="AI4" s="11">
+      <c r="AJ4" s="10">
         <v>70.0</v>
       </c>
-      <c r="AJ4" s="11">
+      <c r="AK4" s="10">
         <v>9387.0</v>
       </c>
-      <c r="AK4" s="11">
+      <c r="AL4" s="10">
         <v>1284.0</v>
       </c>
-      <c r="AL4" s="11">
+      <c r="AM4" s="10">
         <v>20721.0</v>
       </c>
-      <c r="AM4" s="11">
+      <c r="AN4" s="10">
         <v>650.0</v>
       </c>
-      <c r="AN4" s="11">
+      <c r="AO4" s="10">
         <v>6856.0</v>
       </c>
-      <c r="AO4" s="11">
+      <c r="AP4" s="10">
         <v>9021.0</v>
       </c>
-      <c r="AP4" s="11">
+      <c r="AQ4" s="10">
         <v>18445.0</v>
       </c>
-      <c r="AQ4" s="11">
+      <c r="AR4" s="10">
         <v>761.0</v>
       </c>
-      <c r="AR4" s="11">
+      <c r="AS4" s="10">
         <v>14289.0</v>
       </c>
-      <c r="AS4" s="11">
+      <c r="AT4" s="10">
         <v>1237.0</v>
       </c>
-      <c r="AT4" s="11">
+      <c r="AU4" s="10">
         <v>7936.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="A5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="6">
+        <v>280541.0</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="10">
+      <c r="D5" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="9">
         <v>6321.0</v>
       </c>
-      <c r="F5" s="10">
+      <c r="G5" s="9">
         <v>13554.0</v>
       </c>
-      <c r="G5" s="11">
+      <c r="H5" s="10">
         <v>7236.0</v>
       </c>
-      <c r="H5" s="11">
+      <c r="I5" s="10">
         <v>6318.0</v>
       </c>
-      <c r="I5" s="11">
+      <c r="J5" s="10">
         <v>609.0</v>
       </c>
-      <c r="J5" s="11">
+      <c r="K5" s="10">
         <v>710.0</v>
       </c>
-      <c r="K5" s="11">
+      <c r="L5" s="10">
         <v>781.0</v>
       </c>
-      <c r="L5" s="11">
+      <c r="M5" s="10">
         <v>822.0</v>
       </c>
-      <c r="M5" s="11">
+      <c r="N5" s="10">
         <v>781.0</v>
       </c>
-      <c r="N5" s="11">
+      <c r="O5" s="10">
         <v>720.0</v>
       </c>
-      <c r="O5" s="11">
+      <c r="P5" s="10">
         <v>790.0</v>
       </c>
-      <c r="P5" s="11">
+      <c r="Q5" s="10">
         <v>880.0</v>
       </c>
-      <c r="Q5" s="11">
+      <c r="R5" s="10">
         <v>1004.0</v>
       </c>
-      <c r="R5" s="11">
+      <c r="S5" s="10">
         <v>1012.0</v>
       </c>
-      <c r="S5" s="11">
+      <c r="T5" s="10">
         <v>932.0</v>
       </c>
-      <c r="T5" s="11">
+      <c r="U5" s="10">
         <v>797.0</v>
       </c>
-      <c r="U5" s="11">
+      <c r="V5" s="10">
         <v>851.0</v>
       </c>
-      <c r="V5" s="11">
+      <c r="W5" s="10">
         <v>727.0</v>
       </c>
-      <c r="W5" s="11">
+      <c r="X5" s="10">
         <v>732.0</v>
       </c>
-      <c r="X5" s="11">
+      <c r="Y5" s="10">
         <v>574.0</v>
       </c>
-      <c r="Y5" s="11">
+      <c r="Z5" s="10">
         <v>394.0</v>
       </c>
-      <c r="Z5" s="11">
+      <c r="AA5" s="10">
         <v>259.0</v>
       </c>
-      <c r="AA5" s="11">
+      <c r="AB5" s="10">
         <v>140.0</v>
       </c>
-      <c r="AB5" s="11">
+      <c r="AC5" s="10">
         <v>36.0</v>
       </c>
-      <c r="AC5" s="11">
+      <c r="AD5" s="10">
         <v>3.0</v>
       </c>
-      <c r="AD5" s="11">
+      <c r="AE5" s="10">
         <v>5466.0</v>
       </c>
-      <c r="AE5" s="11">
+      <c r="AF5" s="10">
         <v>53.0</v>
       </c>
-      <c r="AF5" s="11">
+      <c r="AG5" s="10">
         <v>7.0</v>
       </c>
-      <c r="AG5" s="11">
+      <c r="AH5" s="10">
         <v>3.0</v>
       </c>
-      <c r="AH5" s="11">
+      <c r="AI5" s="10">
         <v>6.0</v>
       </c>
-      <c r="AI5" s="11">
+      <c r="AJ5" s="10">
         <v>33.0</v>
       </c>
-      <c r="AJ5" s="11">
+      <c r="AK5" s="10">
         <v>5227.0</v>
       </c>
-      <c r="AK5" s="11">
+      <c r="AL5" s="10">
         <v>341.0</v>
       </c>
-      <c r="AL5" s="11">
+      <c r="AM5" s="10">
         <v>12426.0</v>
       </c>
-      <c r="AM5" s="11">
+      <c r="AN5" s="10">
         <v>176.0</v>
       </c>
-      <c r="AN5" s="11">
+      <c r="AO5" s="10">
         <v>952.0</v>
       </c>
-      <c r="AO5" s="11">
+      <c r="AP5" s="10">
         <v>4000.0</v>
       </c>
-      <c r="AP5" s="11">
+      <c r="AQ5" s="10">
         <v>8923.0</v>
       </c>
-      <c r="AQ5" s="11">
+      <c r="AR5" s="10">
         <v>631.0</v>
       </c>
-      <c r="AR5" s="11">
+      <c r="AS5" s="10">
         <v>6897.0</v>
       </c>
-      <c r="AS5" s="11">
+      <c r="AT5" s="10">
         <v>646.0</v>
       </c>
-      <c r="AT5" s="11">
+      <c r="AU5" s="10">
         <v>4077.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="A6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="6">
+        <v>280541.0</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="10">
+      <c r="D6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="9">
         <v>14580.0</v>
       </c>
-      <c r="F6" s="10">
+      <c r="G6" s="9">
         <v>34797.0</v>
       </c>
-      <c r="G6" s="11">
+      <c r="H6" s="10">
         <v>18277.0</v>
       </c>
-      <c r="H6" s="11">
+      <c r="I6" s="10">
         <v>16520.0</v>
       </c>
-      <c r="I6" s="11">
+      <c r="J6" s="10">
         <v>1502.0</v>
       </c>
-      <c r="J6" s="11">
+      <c r="K6" s="10">
         <v>2037.0</v>
       </c>
-      <c r="K6" s="11">
+      <c r="L6" s="10">
         <v>2099.0</v>
       </c>
-      <c r="L6" s="11">
+      <c r="M6" s="10">
         <v>2258.0</v>
       </c>
-      <c r="M6" s="11">
+      <c r="N6" s="10">
         <v>2169.0</v>
       </c>
-      <c r="N6" s="11">
+      <c r="O6" s="10">
         <v>2158.0</v>
       </c>
-      <c r="O6" s="11">
+      <c r="P6" s="10">
         <v>2461.0</v>
       </c>
-      <c r="P6" s="11">
+      <c r="Q6" s="10">
         <v>2584.0</v>
       </c>
-      <c r="Q6" s="11">
+      <c r="R6" s="10">
         <v>2800.0</v>
       </c>
-      <c r="R6" s="11">
+      <c r="S6" s="10">
         <v>2539.0</v>
       </c>
-      <c r="S6" s="11">
+      <c r="T6" s="10">
         <v>2346.0</v>
       </c>
-      <c r="T6" s="11">
+      <c r="U6" s="10">
         <v>1963.0</v>
       </c>
-      <c r="U6" s="11">
+      <c r="V6" s="10">
         <v>1877.0</v>
       </c>
-      <c r="V6" s="11">
+      <c r="W6" s="10">
         <v>1705.0</v>
       </c>
-      <c r="W6" s="11">
+      <c r="X6" s="10">
         <v>1490.0</v>
       </c>
-      <c r="X6" s="11">
+      <c r="Y6" s="10">
         <v>1163.0</v>
       </c>
-      <c r="Y6" s="11">
+      <c r="Z6" s="10">
         <v>815.0</v>
       </c>
-      <c r="Z6" s="11">
+      <c r="AA6" s="10">
         <v>542.0</v>
       </c>
-      <c r="AA6" s="11">
+      <c r="AB6" s="10">
         <v>222.0</v>
       </c>
-      <c r="AB6" s="11">
+      <c r="AC6" s="10">
         <v>63.0</v>
       </c>
-      <c r="AC6" s="11">
+      <c r="AD6" s="10">
         <v>4.0</v>
       </c>
-      <c r="AD6" s="11">
+      <c r="AE6" s="10">
         <v>13481.0</v>
       </c>
-      <c r="AE6" s="11">
+      <c r="AF6" s="10">
         <v>45.0</v>
       </c>
-      <c r="AF6" s="11">
+      <c r="AG6" s="10">
         <v>4.0</v>
       </c>
-      <c r="AG6" s="11">
+      <c r="AH6" s="10">
         <v>3.0</v>
       </c>
-      <c r="AH6" s="11">
+      <c r="AI6" s="10">
         <v>12.0</v>
       </c>
-      <c r="AI6" s="11">
+      <c r="AJ6" s="10">
         <v>100.0</v>
       </c>
-      <c r="AJ6" s="11">
+      <c r="AK6" s="10">
         <v>12097.0</v>
       </c>
-      <c r="AK6" s="11">
+      <c r="AL6" s="10">
         <v>1548.0</v>
       </c>
-      <c r="AL6" s="11">
+      <c r="AM6" s="10">
         <v>26894.0</v>
       </c>
-      <c r="AM6" s="11">
+      <c r="AN6" s="10">
         <v>640.0</v>
       </c>
-      <c r="AN6" s="11">
+      <c r="AO6" s="10">
         <v>7263.0</v>
       </c>
-      <c r="AO6" s="11">
+      <c r="AP6" s="10">
         <v>10561.0</v>
       </c>
-      <c r="AP6" s="11">
+      <c r="AQ6" s="10">
         <v>23259.0</v>
       </c>
-      <c r="AQ6" s="11">
+      <c r="AR6" s="10">
         <v>977.0</v>
       </c>
-      <c r="AR6" s="11">
+      <c r="AS6" s="10">
         <v>17970.0</v>
       </c>
-      <c r="AS6" s="11">
+      <c r="AT6" s="10">
         <v>1656.0</v>
       </c>
-      <c r="AT6" s="11">
+      <c r="AU6" s="10">
         <v>9979.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="A7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="6">
+        <v>280541.0</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="10">
+      <c r="D7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="9">
         <v>36530.0</v>
       </c>
-      <c r="F7" s="10">
+      <c r="G7" s="9">
         <v>77296.0</v>
       </c>
-      <c r="G7" s="11">
+      <c r="H7" s="10">
         <v>41612.0</v>
       </c>
-      <c r="H7" s="11">
+      <c r="I7" s="10">
         <v>35684.0</v>
       </c>
-      <c r="I7" s="11">
+      <c r="J7" s="10">
         <v>3189.0</v>
       </c>
-      <c r="J7" s="11">
+      <c r="K7" s="10">
         <v>4075.0</v>
       </c>
-      <c r="K7" s="11">
+      <c r="L7" s="10">
         <v>4323.0</v>
       </c>
-      <c r="L7" s="11">
+      <c r="M7" s="10">
         <v>4756.0</v>
       </c>
-      <c r="M7" s="11">
+      <c r="N7" s="10">
         <v>4384.0</v>
       </c>
-      <c r="N7" s="11">
+      <c r="O7" s="10">
         <v>4234.0</v>
       </c>
-      <c r="O7" s="11">
+      <c r="P7" s="10">
         <v>4857.0</v>
       </c>
-      <c r="P7" s="11">
+      <c r="Q7" s="10">
         <v>5339.0</v>
       </c>
-      <c r="Q7" s="11">
+      <c r="R7" s="10">
         <v>5690.0</v>
       </c>
-      <c r="R7" s="11">
+      <c r="S7" s="10">
         <v>5942.0</v>
       </c>
-      <c r="S7" s="11">
+      <c r="T7" s="10">
         <v>5183.0</v>
       </c>
-      <c r="T7" s="11">
+      <c r="U7" s="10">
         <v>4895.0</v>
       </c>
-      <c r="U7" s="11">
+      <c r="V7" s="10">
         <v>4784.0</v>
       </c>
-      <c r="V7" s="11">
+      <c r="W7" s="10">
         <v>4171.0</v>
       </c>
-      <c r="W7" s="11">
+      <c r="X7" s="10">
         <v>3954.0</v>
       </c>
-      <c r="X7" s="11">
+      <c r="Y7" s="10">
         <v>3132.0</v>
       </c>
-      <c r="Y7" s="11">
+      <c r="Z7" s="10">
         <v>2118.0</v>
       </c>
-      <c r="Z7" s="11">
+      <c r="AA7" s="10">
         <v>1308.0</v>
       </c>
-      <c r="AA7" s="11">
+      <c r="AB7" s="10">
         <v>701.0</v>
       </c>
-      <c r="AB7" s="11">
+      <c r="AC7" s="10">
         <v>240.0</v>
       </c>
-      <c r="AC7" s="11">
+      <c r="AD7" s="10">
         <v>21.0</v>
       </c>
-      <c r="AD7" s="11">
+      <c r="AE7" s="10">
         <v>32425.0</v>
       </c>
-      <c r="AE7" s="11">
+      <c r="AF7" s="10">
         <v>128.0</v>
       </c>
-      <c r="AF7" s="11">
+      <c r="AG7" s="10">
         <v>19.0</v>
       </c>
-      <c r="AG7" s="11">
+      <c r="AH7" s="10">
         <v>9.0</v>
       </c>
-      <c r="AH7" s="11">
+      <c r="AI7" s="10">
         <v>22.0</v>
       </c>
-      <c r="AI7" s="11">
+      <c r="AJ7" s="10">
         <v>179.0</v>
       </c>
-      <c r="AJ7" s="11">
+      <c r="AK7" s="10">
         <v>30431.0</v>
       </c>
-      <c r="AK7" s="11">
+      <c r="AL7" s="10">
         <v>2351.0</v>
       </c>
-      <c r="AL7" s="11">
+      <c r="AM7" s="10">
         <v>68629.0</v>
       </c>
-      <c r="AM7" s="11">
+      <c r="AN7" s="10">
         <v>1068.0</v>
       </c>
-      <c r="AN7" s="11">
+      <c r="AO7" s="10">
         <v>7599.0</v>
       </c>
-      <c r="AO7" s="11">
+      <c r="AP7" s="10">
         <v>22946.0</v>
       </c>
-      <c r="AP7" s="11">
+      <c r="AQ7" s="10">
         <v>52574.0</v>
       </c>
-      <c r="AQ7" s="11">
+      <c r="AR7" s="10">
         <v>1776.0</v>
       </c>
-      <c r="AR7" s="11">
+      <c r="AS7" s="10">
         <v>40877.0</v>
       </c>
-      <c r="AS7" s="11">
+      <c r="AT7" s="10">
         <v>2988.0</v>
       </c>
-      <c r="AT7" s="11">
+      <c r="AU7" s="10">
         <v>22731.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="10">
+      <c r="A8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="6">
+        <v>280541.0</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="9">
         <v>12830.0</v>
       </c>
-      <c r="F8" s="10">
+      <c r="G8" s="9">
         <v>24790.0</v>
       </c>
-      <c r="G8" s="11">
+      <c r="H8" s="10">
         <v>13371.0</v>
       </c>
-      <c r="H8" s="11">
+      <c r="I8" s="10">
         <v>11419.0</v>
       </c>
-      <c r="I8" s="11">
+      <c r="J8" s="10">
         <v>1080.0</v>
       </c>
-      <c r="J8" s="11">
+      <c r="K8" s="10">
         <v>1188.0</v>
       </c>
-      <c r="K8" s="11">
+      <c r="L8" s="10">
         <v>1363.0</v>
       </c>
-      <c r="L8" s="11">
+      <c r="M8" s="10">
         <v>1361.0</v>
       </c>
-      <c r="M8" s="11">
+      <c r="N8" s="10">
         <v>1340.0</v>
       </c>
-      <c r="N8" s="11">
+      <c r="O8" s="10">
         <v>1506.0</v>
       </c>
-      <c r="O8" s="11">
+      <c r="P8" s="10">
         <v>1704.0</v>
       </c>
-      <c r="P8" s="11">
+      <c r="Q8" s="10">
         <v>1818.0</v>
       </c>
-      <c r="Q8" s="11">
+      <c r="R8" s="10">
         <v>1753.0</v>
       </c>
-      <c r="R8" s="11">
+      <c r="S8" s="10">
         <v>1740.0</v>
       </c>
-      <c r="S8" s="11">
+      <c r="T8" s="10">
         <v>1616.0</v>
       </c>
-      <c r="T8" s="11">
+      <c r="U8" s="10">
         <v>1537.0</v>
       </c>
-      <c r="U8" s="11">
+      <c r="V8" s="10">
         <v>1454.0</v>
       </c>
-      <c r="V8" s="11">
+      <c r="W8" s="10">
         <v>1306.0</v>
       </c>
-      <c r="W8" s="11">
+      <c r="X8" s="10">
         <v>1336.0</v>
       </c>
-      <c r="X8" s="11">
+      <c r="Y8" s="10">
         <v>1154.0</v>
       </c>
-      <c r="Y8" s="11">
+      <c r="Z8" s="10">
         <v>780.0</v>
       </c>
-      <c r="Z8" s="11">
+      <c r="AA8" s="10">
         <v>456.0</v>
       </c>
-      <c r="AA8" s="11">
+      <c r="AB8" s="10">
         <v>232.0</v>
       </c>
-      <c r="AB8" s="11">
+      <c r="AC8" s="10">
         <v>56.0</v>
       </c>
-      <c r="AC8" s="11">
+      <c r="AD8" s="10">
         <v>10.0</v>
       </c>
-      <c r="AD8" s="11">
+      <c r="AE8" s="10">
         <v>11192.0</v>
       </c>
-      <c r="AE8" s="11">
+      <c r="AF8" s="10">
         <v>42.0</v>
       </c>
-      <c r="AF8" s="11">
+      <c r="AG8" s="10">
         <v>7.0</v>
       </c>
-      <c r="AG8" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH8" s="11">
+      <c r="AH8" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI8" s="10">
         <v>8.0</v>
       </c>
-      <c r="AI8" s="11">
+      <c r="AJ8" s="10">
         <v>62.0</v>
       </c>
-      <c r="AJ8" s="11">
+      <c r="AK8" s="10">
         <v>10646.0</v>
       </c>
-      <c r="AK8" s="11">
+      <c r="AL8" s="10">
         <v>665.0</v>
       </c>
-      <c r="AL8" s="11">
+      <c r="AM8" s="10">
         <v>22935.0</v>
       </c>
-      <c r="AM8" s="11">
+      <c r="AN8" s="10">
         <v>280.0</v>
       </c>
-      <c r="AN8" s="11">
+      <c r="AO8" s="10">
         <v>1575.0</v>
       </c>
-      <c r="AO8" s="11">
+      <c r="AP8" s="10">
         <v>7292.0</v>
       </c>
-      <c r="AP8" s="11">
+      <c r="AQ8" s="10">
         <v>16669.0</v>
       </c>
-      <c r="AQ8" s="11">
+      <c r="AR8" s="10">
         <v>829.0</v>
       </c>
-      <c r="AR8" s="11">
+      <c r="AS8" s="10">
         <v>13177.0</v>
       </c>
-      <c r="AS8" s="11">
+      <c r="AT8" s="10">
         <v>844.0</v>
       </c>
-      <c r="AT8" s="11">
+      <c r="AU8" s="10">
         <v>7418.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="A9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="6">
+        <v>280541.0</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="10">
+      <c r="D9" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="9">
         <v>3657.0</v>
       </c>
-      <c r="F9" s="10">
+      <c r="G9" s="9">
         <v>8707.0</v>
       </c>
-      <c r="G9" s="11">
+      <c r="H9" s="10">
         <v>4609.0</v>
       </c>
-      <c r="H9" s="11">
+      <c r="I9" s="10">
         <v>4098.0</v>
       </c>
-      <c r="I9" s="11">
+      <c r="J9" s="10">
         <v>334.0</v>
       </c>
-      <c r="J9" s="11">
+      <c r="K9" s="10">
         <v>498.0</v>
       </c>
-      <c r="K9" s="11">
+      <c r="L9" s="10">
         <v>544.0</v>
       </c>
-      <c r="L9" s="11">
+      <c r="M9" s="10">
         <v>556.0</v>
       </c>
-      <c r="M9" s="11">
+      <c r="N9" s="10">
         <v>526.0</v>
       </c>
-      <c r="N9" s="11">
+      <c r="O9" s="10">
         <v>489.0</v>
       </c>
-      <c r="O9" s="11">
+      <c r="P9" s="10">
         <v>532.0</v>
       </c>
-      <c r="P9" s="11">
+      <c r="Q9" s="10">
         <v>619.0</v>
       </c>
-      <c r="Q9" s="11">
+      <c r="R9" s="10">
         <v>739.0</v>
       </c>
-      <c r="R9" s="11">
+      <c r="S9" s="10">
         <v>687.0</v>
       </c>
-      <c r="S9" s="11">
+      <c r="T9" s="10">
         <v>610.0</v>
       </c>
-      <c r="T9" s="11">
+      <c r="U9" s="10">
         <v>486.0</v>
       </c>
-      <c r="U9" s="11">
+      <c r="V9" s="10">
         <v>487.0</v>
       </c>
-      <c r="V9" s="11">
+      <c r="W9" s="10">
         <v>457.0</v>
       </c>
-      <c r="W9" s="11">
+      <c r="X9" s="10">
         <v>428.0</v>
       </c>
-      <c r="X9" s="11">
+      <c r="Y9" s="10">
         <v>306.0</v>
       </c>
-      <c r="Y9" s="11">
+      <c r="Z9" s="10">
         <v>207.0</v>
       </c>
-      <c r="Z9" s="11">
+      <c r="AA9" s="10">
         <v>130.0</v>
       </c>
-      <c r="AA9" s="11">
+      <c r="AB9" s="10">
         <v>57.0</v>
       </c>
-      <c r="AB9" s="11">
+      <c r="AC9" s="10">
         <v>14.0</v>
       </c>
-      <c r="AC9" s="11">
+      <c r="AD9" s="10">
         <v>1.0</v>
       </c>
-      <c r="AD9" s="11">
+      <c r="AE9" s="10">
         <v>3377.0</v>
       </c>
-      <c r="AE9" s="11">
+      <c r="AF9" s="10">
         <v>15.0</v>
       </c>
-      <c r="AF9" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG9" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH9" s="11">
+      <c r="AG9" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH9" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI9" s="10">
         <v>1.0</v>
       </c>
-      <c r="AI9" s="11">
+      <c r="AJ9" s="10">
         <v>20.0</v>
       </c>
-      <c r="AJ9" s="11">
+      <c r="AK9" s="10">
         <v>3086.0</v>
       </c>
-      <c r="AK9" s="11">
+      <c r="AL9" s="10">
         <v>327.0</v>
       </c>
-      <c r="AL9" s="11">
+      <c r="AM9" s="10">
         <v>7162.0</v>
       </c>
-      <c r="AM9" s="11">
+      <c r="AN9" s="10">
         <v>139.0</v>
       </c>
-      <c r="AN9" s="11">
+      <c r="AO9" s="10">
         <v>1406.0</v>
       </c>
-      <c r="AO9" s="11">
+      <c r="AP9" s="10">
         <v>2665.0</v>
       </c>
-      <c r="AP9" s="11">
+      <c r="AQ9" s="10">
         <v>5787.0</v>
       </c>
-      <c r="AQ9" s="11">
+      <c r="AR9" s="10">
         <v>255.0</v>
       </c>
-      <c r="AR9" s="11">
+      <c r="AS9" s="10">
         <v>4455.0</v>
       </c>
-      <c r="AS9" s="11">
+      <c r="AT9" s="10">
         <v>408.0</v>
       </c>
-      <c r="AT9" s="11">
+      <c r="AU9" s="10">
         <v>2587.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="A10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="6">
+        <v>280541.0</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="10">
+      <c r="D10" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="9">
         <v>11030.0</v>
       </c>
-      <c r="F10" s="10">
+      <c r="G10" s="9">
         <v>26720.0</v>
       </c>
-      <c r="G10" s="11">
+      <c r="H10" s="10">
         <v>14017.0</v>
       </c>
-      <c r="H10" s="11">
+      <c r="I10" s="10">
         <v>12703.0</v>
       </c>
-      <c r="I10" s="11">
+      <c r="J10" s="10">
         <v>1210.0</v>
       </c>
-      <c r="J10" s="11">
+      <c r="K10" s="10">
         <v>1609.0</v>
       </c>
-      <c r="K10" s="11">
+      <c r="L10" s="10">
         <v>1728.0</v>
       </c>
-      <c r="L10" s="11">
+      <c r="M10" s="10">
         <v>1811.0</v>
       </c>
-      <c r="M10" s="11">
+      <c r="N10" s="10">
         <v>1699.0</v>
       </c>
-      <c r="N10" s="11">
+      <c r="O10" s="10">
         <v>1726.0</v>
       </c>
-      <c r="O10" s="11">
+      <c r="P10" s="10">
         <v>1876.0</v>
       </c>
-      <c r="P10" s="11">
+      <c r="Q10" s="10">
         <v>1818.0</v>
       </c>
-      <c r="Q10" s="11">
+      <c r="R10" s="10">
         <v>1983.0</v>
       </c>
-      <c r="R10" s="11">
+      <c r="S10" s="10">
         <v>1911.0</v>
       </c>
-      <c r="S10" s="11">
+      <c r="T10" s="10">
         <v>1619.0</v>
       </c>
-      <c r="T10" s="11">
+      <c r="U10" s="10">
         <v>1564.0</v>
       </c>
-      <c r="U10" s="11">
+      <c r="V10" s="10">
         <v>1466.0</v>
       </c>
-      <c r="V10" s="11">
+      <c r="W10" s="10">
         <v>1266.0</v>
       </c>
-      <c r="W10" s="11">
+      <c r="X10" s="10">
         <v>1154.0</v>
       </c>
-      <c r="X10" s="11">
+      <c r="Y10" s="10">
         <v>952.0</v>
       </c>
-      <c r="Y10" s="11">
+      <c r="Z10" s="10">
         <v>628.0</v>
       </c>
-      <c r="Z10" s="11">
+      <c r="AA10" s="10">
         <v>429.0</v>
       </c>
-      <c r="AA10" s="11">
+      <c r="AB10" s="10">
         <v>222.0</v>
       </c>
-      <c r="AB10" s="11">
+      <c r="AC10" s="10">
         <v>43.0</v>
       </c>
-      <c r="AC10" s="11">
+      <c r="AD10" s="10">
         <v>6.0</v>
       </c>
-      <c r="AD10" s="11">
+      <c r="AE10" s="10">
         <v>9904.0</v>
       </c>
-      <c r="AE10" s="11">
+      <c r="AF10" s="10">
         <v>160.0</v>
       </c>
-      <c r="AF10" s="11">
+      <c r="AG10" s="10">
         <v>11.0</v>
       </c>
-      <c r="AG10" s="11">
+      <c r="AH10" s="10">
         <v>13.0</v>
       </c>
-      <c r="AH10" s="11">
+      <c r="AI10" s="10">
         <v>10.0</v>
       </c>
-      <c r="AI10" s="11">
+      <c r="AJ10" s="10">
         <v>88.0</v>
       </c>
-      <c r="AJ10" s="11">
+      <c r="AK10" s="10">
         <v>8971.0</v>
       </c>
-      <c r="AK10" s="11">
+      <c r="AL10" s="10">
         <v>1215.0</v>
       </c>
-      <c r="AL10" s="11">
+      <c r="AM10" s="10">
         <v>20368.0</v>
       </c>
-      <c r="AM10" s="11">
+      <c r="AN10" s="10">
         <v>580.0</v>
       </c>
-      <c r="AN10" s="11">
+      <c r="AO10" s="10">
         <v>5772.0</v>
       </c>
-      <c r="AO10" s="11">
+      <c r="AP10" s="10">
         <v>8290.0</v>
       </c>
-      <c r="AP10" s="11">
+      <c r="AQ10" s="10">
         <v>17336.0</v>
       </c>
-      <c r="AQ10" s="11">
+      <c r="AR10" s="10">
         <v>1094.0</v>
       </c>
-      <c r="AR10" s="11">
+      <c r="AS10" s="10">
         <v>13358.0</v>
       </c>
-      <c r="AS10" s="11">
+      <c r="AT10" s="10">
         <v>1249.0</v>
       </c>
-      <c r="AT10" s="11">
+      <c r="AU10" s="10">
         <v>7923.0</v>
       </c>
     </row>
